--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122319415</v>
+        <v>122319351</v>
       </c>
       <c r="B2" t="n">
-        <v>110312</v>
+        <v>98175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697258</v>
+        <v>697254</v>
       </c>
       <c r="R2" t="n">
-        <v>6557147</v>
+        <v>6557157</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122318867</v>
+        <v>122318956</v>
       </c>
       <c r="B3" t="n">
-        <v>97129</v>
+        <v>90799</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697230</v>
+        <v>697249</v>
       </c>
       <c r="R3" t="n">
-        <v>6557010</v>
+        <v>6557062</v>
       </c>
       <c r="S3" t="n">
         <v>12</v>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122319726</v>
+        <v>122319074</v>
       </c>
       <c r="B4" t="n">
-        <v>98175</v>
+        <v>4776</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,31 +922,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697259</v>
+        <v>697255</v>
       </c>
       <c r="R4" t="n">
-        <v>6557169</v>
+        <v>6557107</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122319795</v>
+        <v>122318867</v>
       </c>
       <c r="B5" t="n">
-        <v>98175</v>
+        <v>97129</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1043,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,13 +1075,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697243</v>
+        <v>697230</v>
       </c>
       <c r="R5" t="n">
-        <v>6557191</v>
+        <v>6557010</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122319351</v>
+        <v>122320250</v>
       </c>
       <c r="B6" t="n">
         <v>98175</v>
@@ -1183,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697254</v>
+        <v>697229</v>
       </c>
       <c r="R6" t="n">
-        <v>6557157</v>
+        <v>6557114</v>
       </c>
       <c r="S6" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319074</v>
+        <v>122319558</v>
       </c>
       <c r="B7" t="n">
-        <v>4776</v>
+        <v>98175</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,36 +1275,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,13 +1307,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697255</v>
+        <v>697235</v>
       </c>
       <c r="R7" t="n">
-        <v>6557107</v>
+        <v>6557123</v>
       </c>
       <c r="S7" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122318956</v>
+        <v>122319322</v>
       </c>
       <c r="B8" t="n">
-        <v>90799</v>
+        <v>98175</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1391,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697249</v>
+        <v>697280</v>
       </c>
       <c r="R8" t="n">
-        <v>6557062</v>
+        <v>6557133</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,7 +1495,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122320250</v>
+        <v>122319726</v>
       </c>
       <c r="B9" t="n">
         <v>98175</v>
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697229</v>
+        <v>697259</v>
       </c>
       <c r="R9" t="n">
-        <v>6557114</v>
+        <v>6557169</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1727,7 +1727,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122319558</v>
+        <v>122319795</v>
       </c>
       <c r="B11" t="n">
         <v>98175</v>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697235</v>
+        <v>697243</v>
       </c>
       <c r="R11" t="n">
-        <v>6557123</v>
+        <v>6557191</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122319322</v>
+        <v>122319415</v>
       </c>
       <c r="B12" t="n">
-        <v>98175</v>
+        <v>110312</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,25 +1855,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697280</v>
+        <v>697258</v>
       </c>
       <c r="R12" t="n">
-        <v>6557133</v>
+        <v>6557147</v>
       </c>
       <c r="S12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122319339</v>
+        <v>122319205</v>
       </c>
       <c r="B13" t="n">
-        <v>98175</v>
+        <v>5172</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,31 +1971,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2003,13 +2004,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>697268</v>
+        <v>697253</v>
       </c>
       <c r="R13" t="n">
-        <v>6557168</v>
+        <v>6557131</v>
       </c>
       <c r="S13" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2038,7 +2039,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,7 +2049,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122319205</v>
+        <v>122319339</v>
       </c>
       <c r="B14" t="n">
-        <v>5172</v>
+        <v>98175</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,32 +2089,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102204</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697253</v>
+        <v>697268</v>
       </c>
       <c r="R14" t="n">
-        <v>6557131</v>
+        <v>6557168</v>
       </c>
       <c r="S14" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122319074</v>
+        <v>122318867</v>
       </c>
       <c r="B4" t="n">
-        <v>4776</v>
+        <v>97129</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,32 +926,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697255</v>
+        <v>697230</v>
       </c>
       <c r="R4" t="n">
-        <v>6557107</v>
+        <v>6557010</v>
       </c>
       <c r="S4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122318867</v>
+        <v>122319074</v>
       </c>
       <c r="B5" t="n">
-        <v>97129</v>
+        <v>4776</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,27 +1042,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697230</v>
+        <v>697255</v>
       </c>
       <c r="R5" t="n">
-        <v>6557010</v>
+        <v>6557107</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122319351</v>
+        <v>122319558</v>
       </c>
       <c r="B2" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697254</v>
+        <v>697235</v>
       </c>
       <c r="R2" t="n">
-        <v>6557157</v>
+        <v>6557123</v>
       </c>
       <c r="S2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122318956</v>
+        <v>122318867</v>
       </c>
       <c r="B3" t="n">
-        <v>90799</v>
+        <v>97139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697249</v>
+        <v>697230</v>
       </c>
       <c r="R3" t="n">
-        <v>6557062</v>
+        <v>6557010</v>
       </c>
       <c r="S3" t="n">
         <v>12</v>
@@ -873,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122318867</v>
+        <v>122319074</v>
       </c>
       <c r="B4" t="n">
-        <v>97129</v>
+        <v>4776</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,27 +923,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697230</v>
+        <v>697255</v>
       </c>
       <c r="R4" t="n">
-        <v>6557010</v>
+        <v>6557107</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122319074</v>
+        <v>122319322</v>
       </c>
       <c r="B5" t="n">
-        <v>4776</v>
+        <v>98185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,36 +1040,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697255</v>
+        <v>697280</v>
       </c>
       <c r="R5" t="n">
-        <v>6557107</v>
+        <v>6557133</v>
       </c>
       <c r="S5" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122320250</v>
+        <v>122318956</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>90809</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,31 +1156,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697229</v>
+        <v>697249</v>
       </c>
       <c r="R6" t="n">
-        <v>6557114</v>
+        <v>6557062</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319558</v>
+        <v>122319351</v>
       </c>
       <c r="B7" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697235</v>
+        <v>697254</v>
       </c>
       <c r="R7" t="n">
-        <v>6557123</v>
+        <v>6557157</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122319322</v>
+        <v>122319380</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697280</v>
+        <v>697263</v>
       </c>
       <c r="R8" t="n">
-        <v>6557133</v>
+        <v>6557128</v>
       </c>
       <c r="S8" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122319726</v>
+        <v>122319795</v>
       </c>
       <c r="B9" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697259</v>
+        <v>697243</v>
       </c>
       <c r="R9" t="n">
-        <v>6557169</v>
+        <v>6557191</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122319380</v>
+        <v>122320250</v>
       </c>
       <c r="B10" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697263</v>
+        <v>697229</v>
       </c>
       <c r="R10" t="n">
-        <v>6557128</v>
+        <v>6557114</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122319795</v>
+        <v>122319415</v>
       </c>
       <c r="B11" t="n">
-        <v>98175</v>
+        <v>110322</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,25 +1739,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697243</v>
+        <v>697258</v>
       </c>
       <c r="R11" t="n">
-        <v>6557191</v>
+        <v>6557147</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122319415</v>
+        <v>122319726</v>
       </c>
       <c r="B12" t="n">
-        <v>110312</v>
+        <v>98185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,25 +1855,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697258</v>
+        <v>697259</v>
       </c>
       <c r="R12" t="n">
-        <v>6557147</v>
+        <v>6557169</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122319205</v>
+        <v>122319339</v>
       </c>
       <c r="B13" t="n">
-        <v>5172</v>
+        <v>98185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,32 +1971,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102204</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2004,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>697253</v>
+        <v>697268</v>
       </c>
       <c r="R13" t="n">
-        <v>6557131</v>
+        <v>6557168</v>
       </c>
       <c r="S13" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2039,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2049,7 +2048,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122319339</v>
+        <v>122319205</v>
       </c>
       <c r="B14" t="n">
-        <v>98175</v>
+        <v>5172</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,31 +2088,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697268</v>
+        <v>697253</v>
       </c>
       <c r="R14" t="n">
-        <v>6557168</v>
+        <v>6557131</v>
       </c>
       <c r="S14" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,7 +2197,7 @@
         <v>122318675</v>
       </c>
       <c r="B15" t="n">
-        <v>97132</v>
+        <v>97142</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122319558</v>
+        <v>122319726</v>
       </c>
       <c r="B2" t="n">
         <v>98185</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697235</v>
+        <v>697259</v>
       </c>
       <c r="R2" t="n">
-        <v>6557123</v>
+        <v>6557169</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122318867</v>
+        <v>122319415</v>
       </c>
       <c r="B3" t="n">
-        <v>97139</v>
+        <v>110322</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697230</v>
+        <v>697258</v>
       </c>
       <c r="R3" t="n">
-        <v>6557010</v>
+        <v>6557147</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1028,7 +1028,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122319322</v>
+        <v>122319380</v>
       </c>
       <c r="B5" t="n">
         <v>98185</v>
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697280</v>
+        <v>697263</v>
       </c>
       <c r="R5" t="n">
-        <v>6557133</v>
+        <v>6557128</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122318956</v>
+        <v>122319795</v>
       </c>
       <c r="B6" t="n">
-        <v>90809</v>
+        <v>98185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,34 +1156,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,13 +1188,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697249</v>
+        <v>697243</v>
       </c>
       <c r="R6" t="n">
-        <v>6557062</v>
+        <v>6557191</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319351</v>
+        <v>122318956</v>
       </c>
       <c r="B7" t="n">
-        <v>98185</v>
+        <v>90809</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,31 +1272,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697254</v>
+        <v>697249</v>
       </c>
       <c r="R7" t="n">
-        <v>6557157</v>
+        <v>6557062</v>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122319380</v>
+        <v>122319351</v>
       </c>
       <c r="B8" t="n">
         <v>98185</v>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697263</v>
+        <v>697254</v>
       </c>
       <c r="R8" t="n">
-        <v>6557128</v>
+        <v>6557157</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,7 +1495,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122319795</v>
+        <v>122320250</v>
       </c>
       <c r="B9" t="n">
         <v>98185</v>
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697243</v>
+        <v>697229</v>
       </c>
       <c r="R9" t="n">
-        <v>6557191</v>
+        <v>6557114</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122320250</v>
+        <v>122318867</v>
       </c>
       <c r="B10" t="n">
-        <v>98185</v>
+        <v>97139</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697229</v>
+        <v>697230</v>
       </c>
       <c r="R10" t="n">
-        <v>6557114</v>
+        <v>6557010</v>
       </c>
       <c r="S10" t="n">
         <v>12</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122319415</v>
+        <v>122319322</v>
       </c>
       <c r="B11" t="n">
-        <v>110322</v>
+        <v>98185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,25 +1739,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697258</v>
+        <v>697280</v>
       </c>
       <c r="R11" t="n">
-        <v>6557147</v>
+        <v>6557133</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,7 +1843,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122319726</v>
+        <v>122319558</v>
       </c>
       <c r="B12" t="n">
         <v>98185</v>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697259</v>
+        <v>697235</v>
       </c>
       <c r="R12" t="n">
-        <v>6557169</v>
+        <v>6557123</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122318956</v>
+        <v>122319351</v>
       </c>
       <c r="B7" t="n">
-        <v>90809</v>
+        <v>98185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,34 +1272,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697249</v>
+        <v>697254</v>
       </c>
       <c r="R7" t="n">
-        <v>6557062</v>
+        <v>6557157</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122319351</v>
+        <v>122318956</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>90809</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,31 +1388,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697254</v>
+        <v>697249</v>
       </c>
       <c r="R8" t="n">
-        <v>6557157</v>
+        <v>6557062</v>
       </c>
       <c r="S8" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122319726</v>
+        <v>122319558</v>
       </c>
       <c r="B2" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697259</v>
+        <v>697235</v>
       </c>
       <c r="R2" t="n">
-        <v>6557169</v>
+        <v>6557123</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122319415</v>
+        <v>122318956</v>
       </c>
       <c r="B3" t="n">
-        <v>110322</v>
+        <v>90821</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697258</v>
+        <v>697249</v>
       </c>
       <c r="R3" t="n">
-        <v>6557147</v>
+        <v>6557062</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122319074</v>
+        <v>122319795</v>
       </c>
       <c r="B4" t="n">
-        <v>4776</v>
+        <v>98197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,36 +922,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697255</v>
+        <v>697243</v>
       </c>
       <c r="R4" t="n">
-        <v>6557107</v>
+        <v>6557191</v>
       </c>
       <c r="S4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122319380</v>
+        <v>122319351</v>
       </c>
       <c r="B5" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697263</v>
+        <v>697254</v>
       </c>
       <c r="R5" t="n">
-        <v>6557128</v>
+        <v>6557157</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122319795</v>
+        <v>122319726</v>
       </c>
       <c r="B6" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697243</v>
+        <v>697259</v>
       </c>
       <c r="R6" t="n">
-        <v>6557191</v>
+        <v>6557169</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319351</v>
+        <v>122319074</v>
       </c>
       <c r="B7" t="n">
-        <v>98185</v>
+        <v>4776</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,31 +1270,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,13 +1307,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697254</v>
+        <v>697255</v>
       </c>
       <c r="R7" t="n">
-        <v>6557157</v>
+        <v>6557107</v>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122318956</v>
+        <v>122319415</v>
       </c>
       <c r="B8" t="n">
-        <v>90809</v>
+        <v>110335</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1391,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697249</v>
+        <v>697258</v>
       </c>
       <c r="R8" t="n">
-        <v>6557062</v>
+        <v>6557147</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122320250</v>
+        <v>122318867</v>
       </c>
       <c r="B9" t="n">
-        <v>98185</v>
+        <v>97151</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,25 +1507,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697229</v>
+        <v>697230</v>
       </c>
       <c r="R9" t="n">
-        <v>6557114</v>
+        <v>6557010</v>
       </c>
       <c r="S9" t="n">
         <v>12</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122318867</v>
+        <v>122319380</v>
       </c>
       <c r="B10" t="n">
-        <v>97139</v>
+        <v>98197</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697230</v>
+        <v>697263</v>
       </c>
       <c r="R10" t="n">
-        <v>6557010</v>
+        <v>6557128</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122319322</v>
+        <v>122320250</v>
       </c>
       <c r="B11" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697280</v>
+        <v>697229</v>
       </c>
       <c r="R11" t="n">
-        <v>6557133</v>
+        <v>6557114</v>
       </c>
       <c r="S11" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122319558</v>
+        <v>122319322</v>
       </c>
       <c r="B12" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697235</v>
+        <v>697280</v>
       </c>
       <c r="R12" t="n">
-        <v>6557123</v>
+        <v>6557133</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,7 +1962,7 @@
         <v>122319339</v>
       </c>
       <c r="B13" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>122318675</v>
       </c>
       <c r="B15" t="n">
-        <v>97142</v>
+        <v>97154</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122319558</v>
+        <v>122319415</v>
       </c>
       <c r="B2" t="n">
-        <v>98197</v>
+        <v>110340</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697235</v>
+        <v>697258</v>
       </c>
       <c r="R2" t="n">
-        <v>6557123</v>
+        <v>6557147</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122318956</v>
+        <v>122319795</v>
       </c>
       <c r="B3" t="n">
-        <v>90821</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697249</v>
+        <v>697243</v>
       </c>
       <c r="R3" t="n">
-        <v>6557062</v>
+        <v>6557191</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122319795</v>
+        <v>122318867</v>
       </c>
       <c r="B4" t="n">
-        <v>98197</v>
+        <v>97156</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697243</v>
+        <v>697230</v>
       </c>
       <c r="R4" t="n">
-        <v>6557191</v>
+        <v>6557010</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122319351</v>
+        <v>122320250</v>
       </c>
       <c r="B5" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697254</v>
+        <v>697229</v>
       </c>
       <c r="R5" t="n">
-        <v>6557157</v>
+        <v>6557114</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122319726</v>
+        <v>122319351</v>
       </c>
       <c r="B6" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697259</v>
+        <v>697254</v>
       </c>
       <c r="R6" t="n">
-        <v>6557169</v>
+        <v>6557157</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319074</v>
+        <v>122319380</v>
       </c>
       <c r="B7" t="n">
-        <v>4776</v>
+        <v>98202</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,36 +1267,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,13 +1299,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697255</v>
+        <v>697263</v>
       </c>
       <c r="R7" t="n">
-        <v>6557107</v>
+        <v>6557128</v>
       </c>
       <c r="S7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122319415</v>
+        <v>122318956</v>
       </c>
       <c r="B8" t="n">
-        <v>110335</v>
+        <v>90828</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,31 +1383,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1423,13 +1418,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697258</v>
+        <v>697249</v>
       </c>
       <c r="R8" t="n">
-        <v>6557147</v>
+        <v>6557062</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122318867</v>
+        <v>122319074</v>
       </c>
       <c r="B9" t="n">
-        <v>97151</v>
+        <v>4776</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,27 +1506,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697230</v>
+        <v>697255</v>
       </c>
       <c r="R9" t="n">
-        <v>6557010</v>
+        <v>6557107</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122319380</v>
+        <v>122319322</v>
       </c>
       <c r="B10" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697263</v>
+        <v>697280</v>
       </c>
       <c r="R10" t="n">
-        <v>6557128</v>
+        <v>6557133</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122320250</v>
+        <v>122319726</v>
       </c>
       <c r="B11" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697229</v>
+        <v>697259</v>
       </c>
       <c r="R11" t="n">
-        <v>6557114</v>
+        <v>6557169</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122319322</v>
+        <v>122319558</v>
       </c>
       <c r="B12" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697280</v>
+        <v>697235</v>
       </c>
       <c r="R12" t="n">
-        <v>6557133</v>
+        <v>6557123</v>
       </c>
       <c r="S12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,7 +1962,7 @@
         <v>122319339</v>
       </c>
       <c r="B13" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>122318675</v>
       </c>
       <c r="B15" t="n">
-        <v>97154</v>
+        <v>97159</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122319415</v>
+        <v>122320250</v>
       </c>
       <c r="B2" t="n">
-        <v>110340</v>
+        <v>98211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sårläka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697258</v>
+        <v>697229</v>
       </c>
       <c r="R2" t="n">
-        <v>6557147</v>
+        <v>6557114</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122319795</v>
+        <v>122319415</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>110349</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +798,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>219711</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697243</v>
+        <v>697258</v>
       </c>
       <c r="R3" t="n">
-        <v>6557191</v>
+        <v>6557147</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122318867</v>
+        <v>122319726</v>
       </c>
       <c r="B4" t="n">
-        <v>97156</v>
+        <v>98211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +909,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697230</v>
+        <v>697259</v>
       </c>
       <c r="R4" t="n">
-        <v>6557010</v>
+        <v>6557169</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122320250</v>
+        <v>122319380</v>
       </c>
       <c r="B5" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,11 +1025,6 @@
       </c>
       <c r="E5" t="n">
         <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1067,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697229</v>
+        <v>697263</v>
       </c>
       <c r="R5" t="n">
-        <v>6557114</v>
+        <v>6557128</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122319351</v>
+        <v>122318956</v>
       </c>
       <c r="B6" t="n">
-        <v>98202</v>
+        <v>90833</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,31 +1131,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1183,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697254</v>
+        <v>697249</v>
       </c>
       <c r="R6" t="n">
-        <v>6557157</v>
+        <v>6557062</v>
       </c>
       <c r="S6" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319380</v>
+        <v>122319074</v>
       </c>
       <c r="B7" t="n">
-        <v>98202</v>
+        <v>4776</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,31 +1245,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>102306</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1299,13 +1277,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697263</v>
+        <v>697255</v>
       </c>
       <c r="R7" t="n">
-        <v>6557128</v>
+        <v>6557107</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122318956</v>
+        <v>122319558</v>
       </c>
       <c r="B8" t="n">
-        <v>90828</v>
+        <v>98211</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1361,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697249</v>
+        <v>697235</v>
       </c>
       <c r="R8" t="n">
-        <v>6557062</v>
+        <v>6557123</v>
       </c>
       <c r="S8" t="n">
         <v>12</v>
@@ -1453,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1433,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122319074</v>
+        <v>122318867</v>
       </c>
       <c r="B9" t="n">
-        <v>4776</v>
+        <v>97165</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,32 +1476,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Granbarkgnagare</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1539,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697255</v>
+        <v>697230</v>
       </c>
       <c r="R9" t="n">
-        <v>6557107</v>
+        <v>6557010</v>
       </c>
       <c r="S9" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122319322</v>
+        <v>122319351</v>
       </c>
       <c r="B10" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,11 +1588,6 @@
       </c>
       <c r="E10" t="n">
         <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1655,13 +1610,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697280</v>
+        <v>697254</v>
       </c>
       <c r="R10" t="n">
-        <v>6557133</v>
+        <v>6557157</v>
       </c>
       <c r="S10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122319726</v>
+        <v>122319795</v>
       </c>
       <c r="B11" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,11 +1699,6 @@
       </c>
       <c r="E11" t="n">
         <v>220787</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1771,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697259</v>
+        <v>697243</v>
       </c>
       <c r="R11" t="n">
-        <v>6557169</v>
+        <v>6557191</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122319558</v>
+        <v>122319322</v>
       </c>
       <c r="B12" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,11 +1810,6 @@
       </c>
       <c r="E12" t="n">
         <v>220787</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1887,13 +1832,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697235</v>
+        <v>697280</v>
       </c>
       <c r="R12" t="n">
-        <v>6557123</v>
+        <v>6557133</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122319339</v>
+        <v>122319205</v>
       </c>
       <c r="B13" t="n">
-        <v>98202</v>
+        <v>5172</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,31 +1916,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>102204</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2003,13 +1944,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>697268</v>
+        <v>697253</v>
       </c>
       <c r="R13" t="n">
-        <v>6557168</v>
+        <v>6557131</v>
       </c>
       <c r="S13" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2038,7 +1979,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,7 +1989,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122319205</v>
+        <v>122319339</v>
       </c>
       <c r="B14" t="n">
-        <v>5172</v>
+        <v>98211</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,32 +2029,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102204</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Grönhjon</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2121,13 +2056,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697253</v>
+        <v>697268</v>
       </c>
       <c r="R14" t="n">
-        <v>6557131</v>
+        <v>6557168</v>
       </c>
       <c r="S14" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2156,7 +2091,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,7 +2101,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,7 +2132,7 @@
         <v>122318675</v>
       </c>
       <c r="B15" t="n">
-        <v>97159</v>
+        <v>97168</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,11 +2146,6 @@
       </c>
       <c r="E15" t="n">
         <v>221946</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2314,6 +2244,1811 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122540899</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5172</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102204</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>697273</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6557108</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122540912</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90833</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>697180</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6557049</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Klen äldre levande tall.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122540913</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4776</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102306</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>697178</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6557046</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122540903</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57395</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>697256</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6557166</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122540909</v>
+      </c>
+      <c r="B20" t="n">
+        <v>94733</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2818</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>697191</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6557038</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122540905</v>
+      </c>
+      <c r="B21" t="n">
+        <v>94983</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2180</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>697222</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6557122</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122540907</v>
+      </c>
+      <c r="B22" t="n">
+        <v>94733</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2818</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>697232</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6557085</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122540904</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4770</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100299</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>697224</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6557123</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122540901</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5193</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>105930</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>697273</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6557108</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122540910</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90833</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5442</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>697191</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6557040</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Äldre levande tall.</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122540906</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8430</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106554</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>697226</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6557113</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Björklåga med barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Betula # Björklåga med barken kvar.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122540916</v>
+      </c>
+      <c r="B27" t="n">
+        <v>94733</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2818</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>697167</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6557035</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122540902</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5489</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>101410</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>697275</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6557207</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Gammal levande tall med flagnad bark.</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122540900</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100526</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>697273</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6557108</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122540915</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4776</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102306</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>697173</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6557042</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122320250</v>
+        <v>122319322</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -714,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697229</v>
+        <v>697280</v>
       </c>
       <c r="R2" t="n">
-        <v>6557114</v>
+        <v>6557133</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122319415</v>
+        <v>122319558</v>
       </c>
       <c r="B3" t="n">
-        <v>110349</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697258</v>
+        <v>697235</v>
       </c>
       <c r="R3" t="n">
-        <v>6557147</v>
+        <v>6557123</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122319726</v>
+        <v>122319415</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>110362</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,20 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219711</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697259</v>
+        <v>697258</v>
       </c>
       <c r="R4" t="n">
-        <v>6557169</v>
+        <v>6557147</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122319380</v>
+        <v>122318867</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>97178</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,20 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697263</v>
+        <v>697230</v>
       </c>
       <c r="R5" t="n">
-        <v>6557128</v>
+        <v>6557010</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122318956</v>
+        <v>122320250</v>
       </c>
       <c r="B6" t="n">
-        <v>90833</v>
+        <v>98224</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,29 +1151,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697249</v>
+        <v>697229</v>
       </c>
       <c r="R6" t="n">
-        <v>6557062</v>
+        <v>6557114</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
@@ -1196,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319074</v>
+        <v>122319380</v>
       </c>
       <c r="B7" t="n">
-        <v>4776</v>
+        <v>98224</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,31 +1267,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1277,13 +1299,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697255</v>
+        <v>697263</v>
       </c>
       <c r="R7" t="n">
-        <v>6557107</v>
+        <v>6557128</v>
       </c>
       <c r="S7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122319558</v>
+        <v>122318956</v>
       </c>
       <c r="B8" t="n">
-        <v>98211</v>
+        <v>90846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,26 +1383,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697235</v>
+        <v>697249</v>
       </c>
       <c r="R8" t="n">
-        <v>6557123</v>
+        <v>6557062</v>
       </c>
       <c r="S8" t="n">
         <v>12</v>
@@ -1423,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1433,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122318867</v>
+        <v>122319351</v>
       </c>
       <c r="B9" t="n">
-        <v>97165</v>
+        <v>98224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,20 +1502,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,13 +1534,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697230</v>
+        <v>697254</v>
       </c>
       <c r="R9" t="n">
-        <v>6557010</v>
+        <v>6557157</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122319351</v>
+        <v>122319726</v>
       </c>
       <c r="B10" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,6 +1623,11 @@
       </c>
       <c r="E10" t="n">
         <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1610,13 +1650,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697254</v>
+        <v>697259</v>
       </c>
       <c r="R10" t="n">
-        <v>6557157</v>
+        <v>6557169</v>
       </c>
       <c r="S10" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122319795</v>
+        <v>122319074</v>
       </c>
       <c r="B11" t="n">
-        <v>98211</v>
+        <v>4776</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,26 +1734,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>102306</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1721,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697243</v>
+        <v>697255</v>
       </c>
       <c r="R11" t="n">
-        <v>6557191</v>
+        <v>6557107</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122319322</v>
+        <v>122319795</v>
       </c>
       <c r="B12" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,6 +1860,11 @@
       </c>
       <c r="E12" t="n">
         <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1832,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697280</v>
+        <v>697243</v>
       </c>
       <c r="R12" t="n">
-        <v>6557133</v>
+        <v>6557191</v>
       </c>
       <c r="S12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122319205</v>
+        <v>122319339</v>
       </c>
       <c r="B13" t="n">
-        <v>5172</v>
+        <v>98224</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1916,27 +1971,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102204</v>
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1944,13 +2003,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>697253</v>
+        <v>697268</v>
       </c>
       <c r="R13" t="n">
-        <v>6557131</v>
+        <v>6557168</v>
       </c>
       <c r="S13" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1979,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1989,7 +2048,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122319339</v>
+        <v>122318675</v>
       </c>
       <c r="B14" t="n">
-        <v>98211</v>
+        <v>97181</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2029,20 +2088,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221946</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2056,13 +2120,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697268</v>
+        <v>697195</v>
       </c>
       <c r="R14" t="n">
-        <v>6557168</v>
+        <v>6557025</v>
       </c>
       <c r="S14" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2091,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2165,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Signalart enligt skyddsvärd skog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,10 +2198,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122318675</v>
+        <v>122540901</v>
       </c>
       <c r="B15" t="n">
-        <v>97168</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,33 +2214,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>105930</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Lekarvik, Srm</t>
+          <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697195</v>
+        <v>697273</v>
       </c>
       <c r="R15" t="n">
-        <v>6557025</v>
+        <v>6557108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2203,7 +2278,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2213,12 +2288,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Signalart enligt skyddsvärd skog.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,29 +2297,48 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540899</v>
+        <v>122540916</v>
       </c>
       <c r="B16" t="n">
-        <v>5172</v>
+        <v>94746</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,38 +2347,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102204</v>
+        <v>2818</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697273</v>
+        <v>697167</v>
       </c>
       <c r="R16" t="n">
-        <v>6557108</v>
+        <v>6557035</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,7 +2410,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2331,7 +2420,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2342,21 +2431,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2373,10 +2447,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122540912</v>
+        <v>122540910</v>
       </c>
       <c r="B17" t="n">
-        <v>90833</v>
+        <v>90846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,6 +2465,11 @@
       <c r="E17" t="n">
         <v>5442</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Porodaedalea pini</t>
@@ -2408,10 +2487,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697180</v>
+        <v>697191</v>
       </c>
       <c r="R17" t="n">
-        <v>6557049</v>
+        <v>6557040</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,7 +2522,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2532,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,6 +2544,11 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
       <c r="AK17" t="inlineStr">
         <is>
           <t>Pinus sylvestris</t>
@@ -2472,12 +2556,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2495,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540913</v>
+        <v>122540912</v>
       </c>
       <c r="B18" t="n">
-        <v>4776</v>
+        <v>90846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,38 +2591,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697178</v>
+        <v>697180</v>
       </c>
       <c r="R18" t="n">
-        <v>6557046</v>
+        <v>6557049</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,7 +2654,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2580,7 +2664,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,19 +2676,24 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2622,10 +2711,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540903</v>
+        <v>122540900</v>
       </c>
       <c r="B19" t="n">
-        <v>57395</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,26 +2723,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2662,10 +2756,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697256</v>
+        <v>697273</v>
       </c>
       <c r="R19" t="n">
-        <v>6557166</v>
+        <v>6557108</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2697,7 +2791,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2707,12 +2801,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2723,6 +2812,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2739,10 +2848,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540909</v>
+        <v>122540907</v>
       </c>
       <c r="B20" t="n">
-        <v>94733</v>
+        <v>94746</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2757,6 +2866,11 @@
       <c r="E20" t="n">
         <v>2818</v>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Herzogiella seligeri</t>
@@ -2774,10 +2888,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697191</v>
+        <v>697232</v>
       </c>
       <c r="R20" t="n">
-        <v>6557038</v>
+        <v>6557085</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2809,7 +2923,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2819,7 +2933,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2846,10 +2960,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540905</v>
+        <v>122540906</v>
       </c>
       <c r="B21" t="n">
-        <v>94983</v>
+        <v>8430</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2862,29 +2976,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>106554</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697222</v>
+        <v>697226</v>
       </c>
       <c r="R21" t="n">
-        <v>6557122</v>
+        <v>6557113</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2916,7 +3040,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2926,7 +3050,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,6 +3061,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Björklåga med barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Betula # Björklåga med barken kvar.</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2953,10 +3097,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540907</v>
+        <v>122540902</v>
       </c>
       <c r="B22" t="n">
-        <v>94733</v>
+        <v>5489</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2965,33 +3109,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2818</v>
+        <v>101410</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697232</v>
+        <v>697275</v>
       </c>
       <c r="R22" t="n">
-        <v>6557085</v>
+        <v>6557207</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3023,7 +3177,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3187,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3044,6 +3198,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Gammal levande tall med flagnad bark.</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3078,6 +3252,11 @@
       <c r="E23" t="n">
         <v>100299</v>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Cacotemnus thomsoni</t>
@@ -3156,6 +3335,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
@@ -3187,10 +3371,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540901</v>
+        <v>122540915</v>
       </c>
       <c r="B24" t="n">
-        <v>5193</v>
+        <v>4776</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3203,16 +3387,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>102306</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3227,10 +3416,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697273</v>
+        <v>697173</v>
       </c>
       <c r="R24" t="n">
-        <v>6557108</v>
+        <v>6557042</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3262,7 +3451,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3272,7 +3461,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,6 +3473,11 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK24" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -3291,12 +3485,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3314,10 +3508,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122540910</v>
+        <v>122540899</v>
       </c>
       <c r="B25" t="n">
-        <v>90833</v>
+        <v>5172</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3330,29 +3524,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>102204</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697191</v>
+        <v>697273</v>
       </c>
       <c r="R25" t="n">
-        <v>6557040</v>
+        <v>6557108</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3384,7 +3588,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3394,7 +3598,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3406,19 +3610,24 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Äldre levande tall.</t>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3436,10 +3645,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540906</v>
+        <v>122540913</v>
       </c>
       <c r="B26" t="n">
-        <v>8430</v>
+        <v>4776</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3452,22 +3661,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>102306</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3476,10 +3690,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697226</v>
+        <v>697178</v>
       </c>
       <c r="R26" t="n">
-        <v>6557113</v>
+        <v>6557046</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3511,7 +3725,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3521,7 +3735,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,19 +3747,24 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Björklåga med barken kvar.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Betula # Björklåga med barken kvar.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3563,10 +3782,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540916</v>
+        <v>122540903</v>
       </c>
       <c r="B27" t="n">
-        <v>94733</v>
+        <v>57399</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3575,33 +3794,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697167</v>
+        <v>697256</v>
       </c>
       <c r="R27" t="n">
-        <v>6557035</v>
+        <v>6557166</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3633,7 +3862,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3643,7 +3872,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3670,50 +3904,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540902</v>
+        <v>122540909</v>
       </c>
       <c r="B28" t="n">
-        <v>5489</v>
+        <v>94746</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101410</v>
+        <v>2818</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697275</v>
+        <v>697191</v>
       </c>
       <c r="R28" t="n">
-        <v>6557207</v>
+        <v>6557038</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3745,7 +3979,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3755,7 +3989,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3766,21 +4000,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Gammal levande tall med flagnad bark.</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3797,14 +4016,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540900</v>
+        <v>122540905</v>
       </c>
       <c r="B29" t="n">
-        <v>5173</v>
+        <v>94996</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3813,34 +4032,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>2180</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697273</v>
+        <v>697222</v>
       </c>
       <c r="R29" t="n">
-        <v>6557108</v>
+        <v>6557122</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +4091,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +4101,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3893,21 +4112,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3921,133 +4125,6 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>122540915</v>
-      </c>
-      <c r="B30" t="n">
-        <v>4776</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>102306</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Microbregma emarginatum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Lekarvik, Ornö, Srm</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>697173</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6557042</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Ornö</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122319322</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122319558</v>
+        <v>122319351</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697235</v>
+        <v>697254</v>
       </c>
       <c r="R3" t="n">
-        <v>6557123</v>
+        <v>6557157</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122319415</v>
+        <v>122318956</v>
       </c>
       <c r="B4" t="n">
-        <v>110362</v>
+        <v>90859</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,31 +919,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697258</v>
+        <v>697249</v>
       </c>
       <c r="R4" t="n">
-        <v>6557147</v>
+        <v>6557062</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122318867</v>
+        <v>122319074</v>
       </c>
       <c r="B5" t="n">
-        <v>97178</v>
+        <v>4776</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,27 +1042,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,13 +1075,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697230</v>
+        <v>697255</v>
       </c>
       <c r="R5" t="n">
-        <v>6557010</v>
+        <v>6557107</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122320250</v>
+        <v>122319795</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697229</v>
+        <v>697243</v>
       </c>
       <c r="R6" t="n">
-        <v>6557114</v>
+        <v>6557191</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319380</v>
+        <v>122319415</v>
       </c>
       <c r="B7" t="n">
-        <v>98224</v>
+        <v>110375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,25 +1275,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,13 +1307,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697263</v>
+        <v>697258</v>
       </c>
       <c r="R7" t="n">
-        <v>6557128</v>
+        <v>6557147</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122318956</v>
+        <v>122318867</v>
       </c>
       <c r="B8" t="n">
-        <v>90846</v>
+        <v>97191</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1391,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,10 +1423,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697249</v>
+        <v>697230</v>
       </c>
       <c r="R8" t="n">
-        <v>6557062</v>
+        <v>6557010</v>
       </c>
       <c r="S8" t="n">
         <v>12</v>
@@ -1453,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122319351</v>
+        <v>122320250</v>
       </c>
       <c r="B9" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,13 +1539,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697254</v>
+        <v>697229</v>
       </c>
       <c r="R9" t="n">
-        <v>6557157</v>
+        <v>6557114</v>
       </c>
       <c r="S9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,7 +1614,7 @@
         <v>122319726</v>
       </c>
       <c r="B10" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1722,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122319074</v>
+        <v>122319380</v>
       </c>
       <c r="B11" t="n">
-        <v>4776</v>
+        <v>98237</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,36 +1739,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697255</v>
+        <v>697263</v>
       </c>
       <c r="R11" t="n">
-        <v>6557107</v>
+        <v>6557128</v>
       </c>
       <c r="S11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122319795</v>
+        <v>122319558</v>
       </c>
       <c r="B12" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697243</v>
+        <v>697235</v>
       </c>
       <c r="R12" t="n">
-        <v>6557191</v>
+        <v>6557123</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,7 +1962,7 @@
         <v>122319339</v>
       </c>
       <c r="B13" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122318675</v>
+        <v>122540903</v>
       </c>
       <c r="B14" t="n">
-        <v>97181</v>
+        <v>57399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,42 +2088,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Lekarvik, Srm</t>
+          <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697195</v>
+        <v>697256</v>
       </c>
       <c r="R14" t="n">
-        <v>6557025</v>
+        <v>6557166</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2155,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,12 +2166,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Signalart enligt skyddsvärd skog.</t>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,29 +2180,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122540901</v>
+        <v>122540907</v>
       </c>
       <c r="B15" t="n">
-        <v>5193</v>
+        <v>94759</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2214,39 +2214,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697273</v>
+        <v>697232</v>
       </c>
       <c r="R15" t="n">
-        <v>6557108</v>
+        <v>6557085</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2278,7 +2273,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2288,7 +2283,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,26 +2294,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2335,10 +2310,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540916</v>
+        <v>122540915</v>
       </c>
       <c r="B16" t="n">
-        <v>94746</v>
+        <v>4776</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2351,34 +2326,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697167</v>
+        <v>697173</v>
       </c>
       <c r="R16" t="n">
-        <v>6557035</v>
+        <v>6557042</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2410,7 +2390,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2420,7 +2400,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,6 +2411,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2447,10 +2447,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122540910</v>
+        <v>122540901</v>
       </c>
       <c r="B17" t="n">
-        <v>90846</v>
+        <v>5193</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2459,38 +2459,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697191</v>
+        <v>697273</v>
       </c>
       <c r="R17" t="n">
-        <v>6557040</v>
+        <v>6557108</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2522,7 +2527,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2532,7 +2537,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2546,22 +2551,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Äldre levande tall.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2579,10 +2584,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540912</v>
+        <v>122540910</v>
       </c>
       <c r="B18" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2619,10 +2624,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697180</v>
+        <v>697191</v>
       </c>
       <c r="R18" t="n">
-        <v>6557049</v>
+        <v>6557040</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2654,7 +2659,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2664,7 +2669,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2688,12 +2693,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2711,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540900</v>
+        <v>122540912</v>
       </c>
       <c r="B19" t="n">
-        <v>5173</v>
+        <v>90859</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2723,43 +2728,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697273</v>
+        <v>697180</v>
       </c>
       <c r="R19" t="n">
-        <v>6557108</v>
+        <v>6557049</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2815,22 +2815,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540907</v>
+        <v>122540904</v>
       </c>
       <c r="B20" t="n">
-        <v>94746</v>
+        <v>4770</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2864,34 +2864,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2818</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697232</v>
+        <v>697224</v>
       </c>
       <c r="R20" t="n">
-        <v>6557085</v>
+        <v>6557123</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2923,7 +2928,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2933,7 +2938,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2944,6 +2949,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2960,10 +2985,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540906</v>
+        <v>122540916</v>
       </c>
       <c r="B21" t="n">
-        <v>8430</v>
+        <v>94759</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2976,39 +3001,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697226</v>
+        <v>697167</v>
       </c>
       <c r="R21" t="n">
-        <v>6557113</v>
+        <v>6557035</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3040,7 +3060,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3050,7 +3070,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3061,26 +3081,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Björklåga med barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Betula # Björklåga med barken kvar.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3097,10 +3097,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540902</v>
+        <v>122540899</v>
       </c>
       <c r="B22" t="n">
-        <v>5489</v>
+        <v>5172</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3113,21 +3113,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101410</v>
+        <v>102204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697275</v>
+        <v>697273</v>
       </c>
       <c r="R22" t="n">
-        <v>6557207</v>
+        <v>6557108</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3201,22 +3201,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Gammal levande tall med flagnad bark.</t>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122540904</v>
+        <v>122540913</v>
       </c>
       <c r="B23" t="n">
-        <v>4770</v>
+        <v>4776</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100299</v>
+        <v>102306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697224</v>
+        <v>697178</v>
       </c>
       <c r="R23" t="n">
-        <v>6557123</v>
+        <v>6557046</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540915</v>
+        <v>122540906</v>
       </c>
       <c r="B24" t="n">
-        <v>4776</v>
+        <v>8430</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3387,27 +3387,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697173</v>
+        <v>697226</v>
       </c>
       <c r="R24" t="n">
-        <v>6557042</v>
+        <v>6557113</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3475,22 +3475,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Betula # Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122540899</v>
+        <v>122540902</v>
       </c>
       <c r="B25" t="n">
-        <v>5172</v>
+        <v>5489</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3524,21 +3524,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102204</v>
+        <v>101410</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697273</v>
+        <v>697275</v>
       </c>
       <c r="R25" t="n">
-        <v>6557108</v>
+        <v>6557207</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3612,22 +3612,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540913</v>
+        <v>122540900</v>
       </c>
       <c r="B26" t="n">
-        <v>4776</v>
+        <v>5173</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3661,21 +3661,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697178</v>
+        <v>697273</v>
       </c>
       <c r="R26" t="n">
-        <v>6557046</v>
+        <v>6557108</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3782,55 +3782,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540903</v>
+        <v>122540905</v>
       </c>
       <c r="B27" t="n">
-        <v>57399</v>
+        <v>95009</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697256</v>
+        <v>697222</v>
       </c>
       <c r="R27" t="n">
-        <v>6557166</v>
+        <v>6557122</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3862,7 +3857,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3872,12 +3867,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3907,7 +3897,7 @@
         <v>122540909</v>
       </c>
       <c r="B28" t="n">
-        <v>94746</v>
+        <v>94759</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4016,14 +4006,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122540905</v>
+        <v>122318675</v>
       </c>
       <c r="B29" t="n">
-        <v>94996</v>
+        <v>97194</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4032,34 +4022,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lekarvik, Ornö, Srm</t>
+          <t>Stora Lekarvik, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697222</v>
+        <v>697195</v>
       </c>
       <c r="R29" t="n">
-        <v>6557122</v>
+        <v>6557025</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4091,7 +4085,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4101,7 +4095,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4110,18 +4104,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122319351</v>
+        <v>122318956</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>90859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697254</v>
+        <v>697249</v>
       </c>
       <c r="R3" t="n">
-        <v>6557157</v>
+        <v>6557062</v>
       </c>
       <c r="S3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122318956</v>
+        <v>122319380</v>
       </c>
       <c r="B4" t="n">
-        <v>90859</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +922,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697249</v>
+        <v>697263</v>
       </c>
       <c r="R4" t="n">
-        <v>6557062</v>
+        <v>6557128</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122319074</v>
+        <v>122319726</v>
       </c>
       <c r="B5" t="n">
-        <v>4776</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,36 +1038,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697255</v>
+        <v>697259</v>
       </c>
       <c r="R5" t="n">
-        <v>6557107</v>
+        <v>6557169</v>
       </c>
       <c r="S5" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122319795</v>
+        <v>122319415</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>110375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,25 +1154,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697243</v>
+        <v>697258</v>
       </c>
       <c r="R6" t="n">
-        <v>6557191</v>
+        <v>6557147</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319415</v>
+        <v>122318867</v>
       </c>
       <c r="B7" t="n">
-        <v>110375</v>
+        <v>97191</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,16 +1274,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1307,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697258</v>
+        <v>697230</v>
       </c>
       <c r="R7" t="n">
-        <v>6557147</v>
+        <v>6557010</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122318867</v>
+        <v>122319558</v>
       </c>
       <c r="B8" t="n">
-        <v>97191</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,25 +1386,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1423,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697230</v>
+        <v>697235</v>
       </c>
       <c r="R8" t="n">
-        <v>6557010</v>
+        <v>6557123</v>
       </c>
       <c r="S8" t="n">
         <v>12</v>
@@ -1458,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122320250</v>
+        <v>122319074</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
+        <v>4776</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,31 +1502,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697229</v>
+        <v>697255</v>
       </c>
       <c r="R9" t="n">
-        <v>6557114</v>
+        <v>6557107</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,7 +1611,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122319726</v>
+        <v>122319795</v>
       </c>
       <c r="B10" t="n">
         <v>98237</v>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697259</v>
+        <v>697243</v>
       </c>
       <c r="R10" t="n">
-        <v>6557169</v>
+        <v>6557191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,7 +1727,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122319380</v>
+        <v>122320250</v>
       </c>
       <c r="B11" t="n">
         <v>98237</v>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697263</v>
+        <v>697229</v>
       </c>
       <c r="R11" t="n">
-        <v>6557128</v>
+        <v>6557114</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,7 +1843,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122319558</v>
+        <v>122319351</v>
       </c>
       <c r="B12" t="n">
         <v>98237</v>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697235</v>
+        <v>697254</v>
       </c>
       <c r="R12" t="n">
-        <v>6557123</v>
+        <v>6557157</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122540903</v>
+        <v>122540900</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,31 +2088,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697256</v>
+        <v>697273</v>
       </c>
       <c r="R14" t="n">
-        <v>6557166</v>
+        <v>6557108</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,12 +2166,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,6 +2177,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2310,10 +2325,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540915</v>
+        <v>122540899</v>
       </c>
       <c r="B16" t="n">
-        <v>4776</v>
+        <v>5172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,25 +2337,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>102204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2355,10 +2370,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697173</v>
+        <v>697273</v>
       </c>
       <c r="R16" t="n">
-        <v>6557042</v>
+        <v>6557108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,7 +2405,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2400,7 +2415,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2424,12 +2439,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2447,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122540901</v>
+        <v>122540903</v>
       </c>
       <c r="B17" t="n">
-        <v>5193</v>
+        <v>57399</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2459,20 +2474,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2483,7 +2498,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2492,10 +2507,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697273</v>
+        <v>697256</v>
       </c>
       <c r="R17" t="n">
-        <v>6557108</v>
+        <v>6557166</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2527,7 +2542,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2537,7 +2552,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2548,26 +2568,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2584,10 +2584,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540910</v>
+        <v>122540906</v>
       </c>
       <c r="B18" t="n">
-        <v>90859</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2596,38 +2596,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697191</v>
+        <v>697226</v>
       </c>
       <c r="R18" t="n">
-        <v>6557040</v>
+        <v>6557113</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2659,7 +2664,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2669,7 +2674,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,22 +2688,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Äldre levande tall.</t>
+          <t>Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
+          <t>Betula # Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2716,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540912</v>
+        <v>122540904</v>
       </c>
       <c r="B19" t="n">
-        <v>90859</v>
+        <v>4770</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,38 +2733,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697180</v>
+        <v>697224</v>
       </c>
       <c r="R19" t="n">
-        <v>6557049</v>
+        <v>6557123</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2791,7 +2801,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2801,7 +2811,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2815,22 +2825,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2848,10 +2858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540904</v>
+        <v>122540915</v>
       </c>
       <c r="B20" t="n">
-        <v>4770</v>
+        <v>4776</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2864,21 +2874,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100299</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2893,10 +2903,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697224</v>
+        <v>697173</v>
       </c>
       <c r="R20" t="n">
-        <v>6557123</v>
+        <v>6557042</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2928,7 +2938,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2938,7 +2948,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2962,12 +2972,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2985,10 +2995,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540916</v>
+        <v>122540913</v>
       </c>
       <c r="B21" t="n">
-        <v>94759</v>
+        <v>4776</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3001,34 +3011,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2818</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697167</v>
+        <v>697178</v>
       </c>
       <c r="R21" t="n">
-        <v>6557035</v>
+        <v>6557046</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3060,7 +3075,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3070,7 +3085,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3081,6 +3096,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3097,10 +3132,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540899</v>
+        <v>122540902</v>
       </c>
       <c r="B22" t="n">
-        <v>5172</v>
+        <v>5489</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3113,21 +3148,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102204</v>
+        <v>101410</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3142,10 +3177,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697273</v>
+        <v>697275</v>
       </c>
       <c r="R22" t="n">
-        <v>6557108</v>
+        <v>6557207</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3177,7 +3212,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3187,7 +3222,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3201,22 +3236,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3234,10 +3269,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122540913</v>
+        <v>122540910</v>
       </c>
       <c r="B23" t="n">
-        <v>4776</v>
+        <v>90859</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3246,43 +3281,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697178</v>
+        <v>697191</v>
       </c>
       <c r="R23" t="n">
-        <v>6557046</v>
+        <v>6557040</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3314,7 +3344,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3324,7 +3354,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3338,22 +3368,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3371,10 +3401,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540906</v>
+        <v>122540912</v>
       </c>
       <c r="B24" t="n">
-        <v>8430</v>
+        <v>90859</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3383,43 +3413,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697226</v>
+        <v>697180</v>
       </c>
       <c r="R24" t="n">
-        <v>6557113</v>
+        <v>6557049</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3451,7 +3476,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3461,7 +3486,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3475,22 +3500,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Björklåga med barken kvar.</t>
+          <t>Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Betula # Björklåga med barken kvar.</t>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3508,10 +3533,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122540902</v>
+        <v>122540901</v>
       </c>
       <c r="B25" t="n">
-        <v>5489</v>
+        <v>5193</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3520,25 +3545,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101410</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3553,10 +3578,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697275</v>
+        <v>697273</v>
       </c>
       <c r="R25" t="n">
-        <v>6557207</v>
+        <v>6557108</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3588,7 +3613,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3598,7 +3623,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3612,22 +3637,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Gammal levande tall med flagnad bark.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3645,10 +3670,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540900</v>
+        <v>122540916</v>
       </c>
       <c r="B26" t="n">
-        <v>5173</v>
+        <v>94759</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3661,39 +3686,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697273</v>
+        <v>697167</v>
       </c>
       <c r="R26" t="n">
-        <v>6557108</v>
+        <v>6557035</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3725,7 +3745,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3735,7 +3755,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3746,26 +3766,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3782,10 +3782,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540905</v>
+        <v>122540909</v>
       </c>
       <c r="B27" t="n">
-        <v>95009</v>
+        <v>94759</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697222</v>
+        <v>697191</v>
       </c>
       <c r="R27" t="n">
-        <v>6557122</v>
+        <v>6557038</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3894,10 +3894,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540909</v>
+        <v>122540905</v>
       </c>
       <c r="B28" t="n">
-        <v>94759</v>
+        <v>95009</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697191</v>
+        <v>697222</v>
       </c>
       <c r="R28" t="n">
-        <v>6557038</v>
+        <v>6557122</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -3132,10 +3132,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540902</v>
+        <v>122540910</v>
       </c>
       <c r="B22" t="n">
-        <v>5489</v>
+        <v>90859</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3148,39 +3148,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101410</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697275</v>
+        <v>697191</v>
       </c>
       <c r="R22" t="n">
-        <v>6557207</v>
+        <v>6557040</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3212,7 +3207,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3222,7 +3217,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3246,12 +3241,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Gammal levande tall med flagnad bark.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3269,10 +3264,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122540910</v>
+        <v>122540902</v>
       </c>
       <c r="B23" t="n">
-        <v>90859</v>
+        <v>5489</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3285,34 +3280,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>101410</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697191</v>
+        <v>697275</v>
       </c>
       <c r="R23" t="n">
-        <v>6557040</v>
+        <v>6557207</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Äldre levande tall.</t>
+          <t>Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122319322</v>
+        <v>122320250</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697280</v>
+        <v>697229</v>
       </c>
       <c r="R2" t="n">
-        <v>6557133</v>
+        <v>6557114</v>
       </c>
       <c r="S2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122318956</v>
+        <v>122319558</v>
       </c>
       <c r="B3" t="n">
-        <v>90859</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697249</v>
+        <v>697235</v>
       </c>
       <c r="R3" t="n">
-        <v>6557062</v>
+        <v>6557123</v>
       </c>
       <c r="S3" t="n">
         <v>12</v>
@@ -873,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122319380</v>
+        <v>122319322</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697263</v>
+        <v>697280</v>
       </c>
       <c r="R4" t="n">
-        <v>6557128</v>
+        <v>6557133</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122319726</v>
+        <v>122319351</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697259</v>
+        <v>697254</v>
       </c>
       <c r="R5" t="n">
-        <v>6557169</v>
+        <v>6557157</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122319415</v>
+        <v>122318867</v>
       </c>
       <c r="B6" t="n">
-        <v>110375</v>
+        <v>97194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,16 +1155,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1186,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697258</v>
+        <v>697230</v>
       </c>
       <c r="R6" t="n">
-        <v>6557147</v>
+        <v>6557010</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122318867</v>
+        <v>122318956</v>
       </c>
       <c r="B7" t="n">
-        <v>97191</v>
+        <v>90853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,31 +1267,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697230</v>
+        <v>697249</v>
       </c>
       <c r="R7" t="n">
-        <v>6557010</v>
+        <v>6557062</v>
       </c>
       <c r="S7" t="n">
         <v>12</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122319558</v>
+        <v>122319726</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697235</v>
+        <v>697259</v>
       </c>
       <c r="R8" t="n">
-        <v>6557123</v>
+        <v>6557169</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1614,7 +1614,7 @@
         <v>122319795</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122320250</v>
+        <v>122319380</v>
       </c>
       <c r="B11" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697229</v>
+        <v>697263</v>
       </c>
       <c r="R11" t="n">
-        <v>6557114</v>
+        <v>6557128</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122319351</v>
+        <v>122319415</v>
       </c>
       <c r="B12" t="n">
-        <v>98237</v>
+        <v>110378</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,25 +1855,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697254</v>
+        <v>697258</v>
       </c>
       <c r="R12" t="n">
-        <v>6557157</v>
+        <v>6557147</v>
       </c>
       <c r="S12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,7 +1962,7 @@
         <v>122319339</v>
       </c>
       <c r="B13" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122540900</v>
+        <v>122540912</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>90853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,43 +2088,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697273</v>
+        <v>697180</v>
       </c>
       <c r="R14" t="n">
-        <v>6557108</v>
+        <v>6557049</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,22 +2175,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2213,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122540907</v>
+        <v>122540902</v>
       </c>
       <c r="B15" t="n">
-        <v>94759</v>
+        <v>5489</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,38 +2220,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>101410</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697232</v>
+        <v>697275</v>
       </c>
       <c r="R15" t="n">
-        <v>6557085</v>
+        <v>6557207</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,6 +2309,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Gammal levande tall med flagnad bark.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2325,10 +2345,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540899</v>
+        <v>122540907</v>
       </c>
       <c r="B16" t="n">
-        <v>5172</v>
+        <v>94761</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,43 +2357,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102204</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697273</v>
+        <v>697232</v>
       </c>
       <c r="R16" t="n">
-        <v>6557108</v>
+        <v>6557085</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,7 +2420,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2415,7 +2430,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,26 +2441,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2462,10 +2457,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122540903</v>
+        <v>122540906</v>
       </c>
       <c r="B17" t="n">
-        <v>57399</v>
+        <v>8430</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,31 +2469,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2507,10 +2502,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697256</v>
+        <v>697226</v>
       </c>
       <c r="R17" t="n">
-        <v>6557166</v>
+        <v>6557113</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2542,7 +2537,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2552,12 +2547,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2568,6 +2558,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Björklåga med barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Betula # Björklåga med barken kvar.</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2584,10 +2594,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540906</v>
+        <v>122540903</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>57399</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2596,31 +2606,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2629,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697226</v>
+        <v>697256</v>
       </c>
       <c r="R18" t="n">
-        <v>6557113</v>
+        <v>6557166</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2664,7 +2674,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2674,7 +2684,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,26 +2700,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Björklåga med barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Betula # Björklåga med barken kvar.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2721,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540904</v>
+        <v>122540916</v>
       </c>
       <c r="B19" t="n">
-        <v>4770</v>
+        <v>94761</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2737,39 +2732,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100299</v>
+        <v>2818</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697224</v>
+        <v>697167</v>
       </c>
       <c r="R19" t="n">
-        <v>6557123</v>
+        <v>6557035</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2801,7 +2791,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2811,7 +2801,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2822,26 +2812,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2858,10 +2828,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540915</v>
+        <v>122540901</v>
       </c>
       <c r="B20" t="n">
-        <v>4776</v>
+        <v>5193</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2874,21 +2844,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2903,10 +2873,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697173</v>
+        <v>697273</v>
       </c>
       <c r="R20" t="n">
-        <v>6557042</v>
+        <v>6557108</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2938,7 +2908,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2948,7 +2918,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2972,12 +2942,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2995,10 +2965,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540913</v>
+        <v>122540910</v>
       </c>
       <c r="B21" t="n">
-        <v>4776</v>
+        <v>90853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3007,43 +2977,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697178</v>
+        <v>697191</v>
       </c>
       <c r="R21" t="n">
-        <v>6557046</v>
+        <v>6557040</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3075,7 +3040,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3085,7 +3050,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3099,22 +3064,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3132,10 +3097,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540910</v>
+        <v>122540913</v>
       </c>
       <c r="B22" t="n">
-        <v>90859</v>
+        <v>4776</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3144,38 +3109,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697191</v>
+        <v>697178</v>
       </c>
       <c r="R22" t="n">
-        <v>6557040</v>
+        <v>6557046</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3207,7 +3177,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3217,7 +3187,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3231,22 +3201,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Äldre levande tall.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3264,10 +3234,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122540902</v>
+        <v>122540904</v>
       </c>
       <c r="B23" t="n">
-        <v>5489</v>
+        <v>4770</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3276,25 +3246,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101410</v>
+        <v>100299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3309,10 +3279,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697275</v>
+        <v>697224</v>
       </c>
       <c r="R23" t="n">
-        <v>6557207</v>
+        <v>6557123</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3344,7 +3314,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3354,7 +3324,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3368,22 +3338,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Gammal levande tall med flagnad bark.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3401,10 +3371,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540912</v>
+        <v>122540900</v>
       </c>
       <c r="B24" t="n">
-        <v>90859</v>
+        <v>5173</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3413,38 +3383,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697180</v>
+        <v>697273</v>
       </c>
       <c r="R24" t="n">
-        <v>6557049</v>
+        <v>6557108</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3476,7 +3451,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3486,7 +3461,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3500,22 +3475,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3533,10 +3508,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122540901</v>
+        <v>122540899</v>
       </c>
       <c r="B25" t="n">
-        <v>5193</v>
+        <v>5172</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3545,25 +3520,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>102204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3647,12 +3622,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3670,10 +3645,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540916</v>
+        <v>122540915</v>
       </c>
       <c r="B26" t="n">
-        <v>94759</v>
+        <v>4776</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3686,34 +3661,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2818</v>
+        <v>102306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697167</v>
+        <v>697173</v>
       </c>
       <c r="R26" t="n">
-        <v>6557035</v>
+        <v>6557042</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3745,7 +3725,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3755,7 +3735,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3766,6 +3746,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3785,7 +3785,7 @@
         <v>122540909</v>
       </c>
       <c r="B27" t="n">
-        <v>94759</v>
+        <v>94761</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>122540905</v>
       </c>
       <c r="B28" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>122318675</v>
       </c>
       <c r="B29" t="n">
-        <v>97194</v>
+        <v>97197</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122320250</v>
+        <v>122318956</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>90853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697229</v>
+        <v>697249</v>
       </c>
       <c r="R2" t="n">
-        <v>6557114</v>
+        <v>6557062</v>
       </c>
       <c r="S2" t="n">
         <v>12</v>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122319558</v>
+        <v>122319415</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>110378</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697235</v>
+        <v>697258</v>
       </c>
       <c r="R3" t="n">
-        <v>6557123</v>
+        <v>6557147</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +910,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122319322</v>
+        <v>122319726</v>
       </c>
       <c r="B4" t="n">
         <v>98240</v>
@@ -951,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697280</v>
+        <v>697259</v>
       </c>
       <c r="R4" t="n">
-        <v>6557133</v>
+        <v>6557169</v>
       </c>
       <c r="S4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122319351</v>
+        <v>122319795</v>
       </c>
       <c r="B5" t="n">
         <v>98240</v>
@@ -1067,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697254</v>
+        <v>697243</v>
       </c>
       <c r="R5" t="n">
-        <v>6557157</v>
+        <v>6557191</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122318867</v>
+        <v>122319322</v>
       </c>
       <c r="B6" t="n">
-        <v>97194</v>
+        <v>98240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,25 +1154,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697230</v>
+        <v>697280</v>
       </c>
       <c r="R6" t="n">
-        <v>6557010</v>
+        <v>6557133</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122318956</v>
+        <v>122319351</v>
       </c>
       <c r="B7" t="n">
-        <v>90853</v>
+        <v>98240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,34 +1270,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697249</v>
+        <v>697254</v>
       </c>
       <c r="R7" t="n">
-        <v>6557062</v>
+        <v>6557157</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122319726</v>
+        <v>122319074</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
+        <v>4776</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,31 +1386,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,13 +1423,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697259</v>
+        <v>697255</v>
       </c>
       <c r="R8" t="n">
-        <v>6557169</v>
+        <v>6557107</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122319074</v>
+        <v>122320250</v>
       </c>
       <c r="B9" t="n">
-        <v>4776</v>
+        <v>98240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,36 +1507,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697255</v>
+        <v>697229</v>
       </c>
       <c r="R9" t="n">
-        <v>6557107</v>
+        <v>6557114</v>
       </c>
       <c r="S9" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,7 +1611,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122319795</v>
+        <v>122319380</v>
       </c>
       <c r="B10" t="n">
         <v>98240</v>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697243</v>
+        <v>697263</v>
       </c>
       <c r="R10" t="n">
-        <v>6557191</v>
+        <v>6557128</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,7 +1727,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122319380</v>
+        <v>122319558</v>
       </c>
       <c r="B11" t="n">
         <v>98240</v>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697263</v>
+        <v>697235</v>
       </c>
       <c r="R11" t="n">
-        <v>6557128</v>
+        <v>6557123</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122319415</v>
+        <v>122318867</v>
       </c>
       <c r="B12" t="n">
-        <v>110378</v>
+        <v>97194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,16 +1859,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219711</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697258</v>
+        <v>697230</v>
       </c>
       <c r="R12" t="n">
-        <v>6557147</v>
+        <v>6557010</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2208,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122540902</v>
+        <v>122540913</v>
       </c>
       <c r="B15" t="n">
-        <v>5489</v>
+        <v>4776</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,25 +2220,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101410</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697275</v>
+        <v>697178</v>
       </c>
       <c r="R15" t="n">
-        <v>6557207</v>
+        <v>6557046</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,22 +2312,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Gammal levande tall med flagnad bark.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540907</v>
+        <v>122540899</v>
       </c>
       <c r="B16" t="n">
-        <v>94761</v>
+        <v>5172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2357,38 +2357,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>102204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697232</v>
+        <v>697273</v>
       </c>
       <c r="R16" t="n">
-        <v>6557085</v>
+        <v>6557108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2420,7 +2425,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2430,7 +2435,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,6 +2446,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2457,10 +2482,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122540906</v>
+        <v>122540916</v>
       </c>
       <c r="B17" t="n">
-        <v>8430</v>
+        <v>94761</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,39 +2498,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697226</v>
+        <v>697167</v>
       </c>
       <c r="R17" t="n">
-        <v>6557113</v>
+        <v>6557035</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2537,7 +2557,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2547,7 +2567,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,26 +2578,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Björklåga med barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Betula # Björklåga med barken kvar.</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540903</v>
+        <v>122540915</v>
       </c>
       <c r="B18" t="n">
-        <v>57399</v>
+        <v>4776</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2606,31 +2606,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697256</v>
+        <v>697173</v>
       </c>
       <c r="R18" t="n">
-        <v>6557166</v>
+        <v>6557042</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2684,12 +2684,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,6 +2695,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2716,10 +2731,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540916</v>
+        <v>122540900</v>
       </c>
       <c r="B19" t="n">
-        <v>94761</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2732,34 +2747,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697167</v>
+        <v>697273</v>
       </c>
       <c r="R19" t="n">
-        <v>6557035</v>
+        <v>6557108</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2791,7 +2811,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2801,7 +2821,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,6 +2832,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2828,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540901</v>
+        <v>122540902</v>
       </c>
       <c r="B20" t="n">
-        <v>5193</v>
+        <v>5489</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2840,25 +2880,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>101410</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2873,10 +2913,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697273</v>
+        <v>697275</v>
       </c>
       <c r="R20" t="n">
-        <v>6557108</v>
+        <v>6557207</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2908,7 +2948,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2918,7 +2958,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2932,22 +2972,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2965,10 +3005,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540910</v>
+        <v>122540906</v>
       </c>
       <c r="B21" t="n">
-        <v>90853</v>
+        <v>8430</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2977,38 +3017,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697191</v>
+        <v>697226</v>
       </c>
       <c r="R21" t="n">
-        <v>6557040</v>
+        <v>6557113</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3040,7 +3085,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3050,7 +3095,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3064,22 +3109,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Äldre levande tall.</t>
+          <t>Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
+          <t>Betula # Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3097,10 +3142,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540913</v>
+        <v>122540901</v>
       </c>
       <c r="B22" t="n">
-        <v>4776</v>
+        <v>5193</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3113,21 +3158,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3142,10 +3187,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697178</v>
+        <v>697273</v>
       </c>
       <c r="R22" t="n">
-        <v>6557046</v>
+        <v>6557108</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3177,7 +3222,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3187,7 +3232,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3211,12 +3256,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3371,10 +3416,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540900</v>
+        <v>122540907</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
+        <v>94761</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3387,39 +3432,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697273</v>
+        <v>697232</v>
       </c>
       <c r="R24" t="n">
-        <v>6557108</v>
+        <v>6557085</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3451,7 +3491,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3461,7 +3501,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3472,26 +3512,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3508,10 +3528,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122540899</v>
+        <v>122540903</v>
       </c>
       <c r="B25" t="n">
-        <v>5172</v>
+        <v>57399</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3524,27 +3544,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102204</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3553,10 +3573,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697273</v>
+        <v>697256</v>
       </c>
       <c r="R25" t="n">
-        <v>6557108</v>
+        <v>6557166</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3588,7 +3608,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3598,7 +3618,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3609,26 +3634,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3645,10 +3650,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540915</v>
+        <v>122540910</v>
       </c>
       <c r="B26" t="n">
-        <v>4776</v>
+        <v>90853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3657,43 +3662,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697173</v>
+        <v>697191</v>
       </c>
       <c r="R26" t="n">
-        <v>6557042</v>
+        <v>6557040</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3749,22 +3749,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122318956</v>
+        <v>122319726</v>
       </c>
       <c r="B2" t="n">
-        <v>90853</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697249</v>
+        <v>697259</v>
       </c>
       <c r="R2" t="n">
-        <v>6557062</v>
+        <v>6557169</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122319415</v>
+        <v>122319795</v>
       </c>
       <c r="B3" t="n">
-        <v>110378</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697258</v>
+        <v>697243</v>
       </c>
       <c r="R3" t="n">
-        <v>6557147</v>
+        <v>6557191</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122319726</v>
+        <v>122318867</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>97195</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697259</v>
+        <v>697230</v>
       </c>
       <c r="R4" t="n">
-        <v>6557169</v>
+        <v>6557010</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122319795</v>
+        <v>122319322</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697243</v>
+        <v>697280</v>
       </c>
       <c r="R5" t="n">
-        <v>6557191</v>
+        <v>6557133</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122319322</v>
+        <v>122320250</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697280</v>
+        <v>697229</v>
       </c>
       <c r="R6" t="n">
-        <v>6557133</v>
+        <v>6557114</v>
       </c>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319351</v>
+        <v>122319074</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
+        <v>4776</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,31 +1267,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697254</v>
+        <v>697255</v>
       </c>
       <c r="R7" t="n">
-        <v>6557157</v>
+        <v>6557107</v>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122319074</v>
+        <v>122318956</v>
       </c>
       <c r="B8" t="n">
-        <v>4776</v>
+        <v>90854</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,25 +1388,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,8 +1416,6 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697255</v>
+        <v>697249</v>
       </c>
       <c r="R8" t="n">
-        <v>6557107</v>
+        <v>6557062</v>
       </c>
       <c r="S8" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122320250</v>
+        <v>122319558</v>
       </c>
       <c r="B9" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697229</v>
+        <v>697235</v>
       </c>
       <c r="R9" t="n">
-        <v>6557114</v>
+        <v>6557123</v>
       </c>
       <c r="S9" t="n">
         <v>12</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122319380</v>
+        <v>122319415</v>
       </c>
       <c r="B10" t="n">
-        <v>98240</v>
+        <v>110379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,25 +1623,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697263</v>
+        <v>697258</v>
       </c>
       <c r="R10" t="n">
-        <v>6557128</v>
+        <v>6557147</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122319558</v>
+        <v>122319380</v>
       </c>
       <c r="B11" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697235</v>
+        <v>697263</v>
       </c>
       <c r="R11" t="n">
-        <v>6557123</v>
+        <v>6557128</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122318867</v>
+        <v>122319351</v>
       </c>
       <c r="B12" t="n">
-        <v>97194</v>
+        <v>98241</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,25 +1855,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697230</v>
+        <v>697254</v>
       </c>
       <c r="R12" t="n">
-        <v>6557010</v>
+        <v>6557157</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,7 +1962,7 @@
         <v>122319339</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122540912</v>
+        <v>122540915</v>
       </c>
       <c r="B14" t="n">
-        <v>90853</v>
+        <v>4776</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,38 +2088,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697180</v>
+        <v>697173</v>
       </c>
       <c r="R14" t="n">
-        <v>6557049</v>
+        <v>6557042</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,7 +2166,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,22 +2180,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2208,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122540913</v>
+        <v>122540901</v>
       </c>
       <c r="B15" t="n">
-        <v>4776</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,21 +2229,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2253,10 +2258,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697178</v>
+        <v>697273</v>
       </c>
       <c r="R15" t="n">
-        <v>6557046</v>
+        <v>6557108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2288,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,7 +2303,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2322,12 +2327,12 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2345,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540899</v>
+        <v>122540902</v>
       </c>
       <c r="B16" t="n">
-        <v>5172</v>
+        <v>5489</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2361,21 +2366,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102204</v>
+        <v>101410</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2390,10 +2395,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697273</v>
+        <v>697275</v>
       </c>
       <c r="R16" t="n">
-        <v>6557108</v>
+        <v>6557207</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2425,7 +2430,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2435,7 +2440,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,22 +2454,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2482,10 +2487,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122540916</v>
+        <v>122540900</v>
       </c>
       <c r="B17" t="n">
-        <v>94761</v>
+        <v>5173</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2498,34 +2503,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697167</v>
+        <v>697273</v>
       </c>
       <c r="R17" t="n">
-        <v>6557035</v>
+        <v>6557108</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2557,7 +2567,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2567,7 +2577,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2578,6 +2588,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2594,10 +2624,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540915</v>
+        <v>122540906</v>
       </c>
       <c r="B18" t="n">
-        <v>4776</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2610,27 +2640,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2639,10 +2669,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697173</v>
+        <v>697226</v>
       </c>
       <c r="R18" t="n">
-        <v>6557042</v>
+        <v>6557113</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2674,7 +2704,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2684,7 +2714,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2698,22 +2728,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Betula # Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2731,10 +2761,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540900</v>
+        <v>122540904</v>
       </c>
       <c r="B19" t="n">
-        <v>5173</v>
+        <v>4770</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2747,21 +2777,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2776,10 +2806,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697273</v>
+        <v>697224</v>
       </c>
       <c r="R19" t="n">
-        <v>6557108</v>
+        <v>6557123</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2811,7 +2841,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2821,7 +2851,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2845,12 +2875,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2868,10 +2898,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540902</v>
+        <v>122540899</v>
       </c>
       <c r="B20" t="n">
-        <v>5489</v>
+        <v>5172</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,21 +2914,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101410</v>
+        <v>102204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2913,10 +2943,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697275</v>
+        <v>697273</v>
       </c>
       <c r="R20" t="n">
-        <v>6557207</v>
+        <v>6557108</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2948,7 +2978,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2958,7 +2988,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2972,22 +3002,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Gammal levande tall med flagnad bark.</t>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3005,10 +3035,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540906</v>
+        <v>122540910</v>
       </c>
       <c r="B21" t="n">
-        <v>8430</v>
+        <v>90854</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3017,43 +3047,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697226</v>
+        <v>697191</v>
       </c>
       <c r="R21" t="n">
-        <v>6557113</v>
+        <v>6557040</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3085,7 +3110,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3095,7 +3120,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3109,22 +3134,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Björklåga med barken kvar.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Betula # Björklåga med barken kvar.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3142,10 +3167,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540901</v>
+        <v>122540903</v>
       </c>
       <c r="B22" t="n">
-        <v>5193</v>
+        <v>57400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3154,20 +3179,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3178,7 +3203,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3187,10 +3212,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697273</v>
+        <v>697256</v>
       </c>
       <c r="R22" t="n">
-        <v>6557108</v>
+        <v>6557166</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3222,7 +3247,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3232,7 +3257,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3243,26 +3273,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3279,10 +3289,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122540904</v>
+        <v>122540916</v>
       </c>
       <c r="B23" t="n">
-        <v>4770</v>
+        <v>94762</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3295,39 +3305,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100299</v>
+        <v>2818</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697224</v>
+        <v>697167</v>
       </c>
       <c r="R23" t="n">
-        <v>6557123</v>
+        <v>6557035</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3359,7 +3364,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3369,7 +3374,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3380,26 +3385,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3416,10 +3401,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540907</v>
+        <v>122540913</v>
       </c>
       <c r="B24" t="n">
-        <v>94761</v>
+        <v>4776</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3432,34 +3417,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2818</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697232</v>
+        <v>697178</v>
       </c>
       <c r="R24" t="n">
-        <v>6557085</v>
+        <v>6557046</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3491,7 +3481,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3501,7 +3491,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3512,6 +3502,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3528,10 +3538,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122540903</v>
+        <v>122540912</v>
       </c>
       <c r="B25" t="n">
-        <v>57399</v>
+        <v>90854</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3544,39 +3554,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697256</v>
+        <v>697180</v>
       </c>
       <c r="R25" t="n">
-        <v>6557166</v>
+        <v>6557049</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3608,7 +3613,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3618,12 +3623,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3634,6 +3634,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Klen äldre levande tall.</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3650,10 +3670,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540910</v>
+        <v>122540907</v>
       </c>
       <c r="B26" t="n">
-        <v>90853</v>
+        <v>94762</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3662,25 +3682,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>2818</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3690,10 +3710,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697191</v>
+        <v>697232</v>
       </c>
       <c r="R26" t="n">
-        <v>6557040</v>
+        <v>6557085</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3725,7 +3745,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3735,7 +3755,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3746,26 +3766,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Äldre levande tall.</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3785,7 +3785,7 @@
         <v>122540909</v>
       </c>
       <c r="B27" t="n">
-        <v>94761</v>
+        <v>94762</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>122540905</v>
       </c>
       <c r="B28" t="n">
-        <v>95011</v>
+        <v>95012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>122318675</v>
       </c>
       <c r="B29" t="n">
-        <v>97197</v>
+        <v>97198</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122319726</v>
+        <v>122319351</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697259</v>
+        <v>697254</v>
       </c>
       <c r="R2" t="n">
-        <v>6557169</v>
+        <v>6557157</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122319795</v>
+        <v>122319322</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697243</v>
+        <v>697280</v>
       </c>
       <c r="R3" t="n">
-        <v>6557191</v>
+        <v>6557133</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
         <v>122318867</v>
       </c>
       <c r="B4" t="n">
-        <v>97195</v>
+        <v>97198</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122319322</v>
+        <v>122319795</v>
       </c>
       <c r="B5" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697280</v>
+        <v>697243</v>
       </c>
       <c r="R5" t="n">
-        <v>6557133</v>
+        <v>6557191</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122320250</v>
+        <v>122319074</v>
       </c>
       <c r="B6" t="n">
-        <v>98241</v>
+        <v>4776</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,31 +1151,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1183,13 +1188,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697229</v>
+        <v>697255</v>
       </c>
       <c r="R6" t="n">
-        <v>6557114</v>
+        <v>6557107</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319074</v>
+        <v>122319380</v>
       </c>
       <c r="B7" t="n">
-        <v>4776</v>
+        <v>98244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,36 +1272,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697255</v>
+        <v>697263</v>
       </c>
       <c r="R7" t="n">
-        <v>6557107</v>
+        <v>6557128</v>
       </c>
       <c r="S7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122318956</v>
+        <v>122319415</v>
       </c>
       <c r="B8" t="n">
-        <v>90854</v>
+        <v>110382</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1388,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1423,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697249</v>
+        <v>697258</v>
       </c>
       <c r="R8" t="n">
-        <v>6557062</v>
+        <v>6557147</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122319558</v>
+        <v>122319726</v>
       </c>
       <c r="B9" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697235</v>
+        <v>697259</v>
       </c>
       <c r="R9" t="n">
-        <v>6557123</v>
+        <v>6557169</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1581,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122319415</v>
+        <v>122318956</v>
       </c>
       <c r="B10" t="n">
-        <v>110379</v>
+        <v>90857</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,31 +1620,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697258</v>
+        <v>697249</v>
       </c>
       <c r="R10" t="n">
-        <v>6557147</v>
+        <v>6557062</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122319380</v>
+        <v>122319558</v>
       </c>
       <c r="B11" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697263</v>
+        <v>697235</v>
       </c>
       <c r="R11" t="n">
-        <v>6557128</v>
+        <v>6557123</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122319351</v>
+        <v>122320250</v>
       </c>
       <c r="B12" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697254</v>
+        <v>697229</v>
       </c>
       <c r="R12" t="n">
-        <v>6557157</v>
+        <v>6557114</v>
       </c>
       <c r="S12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,7 +1962,7 @@
         <v>122319339</v>
       </c>
       <c r="B13" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122540915</v>
+        <v>122540900</v>
       </c>
       <c r="B14" t="n">
-        <v>4776</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2092,21 +2092,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697173</v>
+        <v>697273</v>
       </c>
       <c r="R14" t="n">
-        <v>6557042</v>
+        <v>6557108</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2213,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122540901</v>
+        <v>122540903</v>
       </c>
       <c r="B15" t="n">
-        <v>5193</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,20 +2225,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2249,7 +2249,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697273</v>
+        <v>697256</v>
       </c>
       <c r="R15" t="n">
-        <v>6557108</v>
+        <v>6557166</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2303,7 +2303,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,26 +2319,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2350,10 +2335,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540902</v>
+        <v>122540899</v>
       </c>
       <c r="B16" t="n">
-        <v>5489</v>
+        <v>5172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,21 +2351,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101410</v>
+        <v>102204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2395,10 +2380,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697275</v>
+        <v>697273</v>
       </c>
       <c r="R16" t="n">
-        <v>6557207</v>
+        <v>6557108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,7 +2415,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2440,7 +2425,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,22 +2439,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Gammal levande tall med flagnad bark.</t>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2487,10 +2472,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122540900</v>
+        <v>122540910</v>
       </c>
       <c r="B17" t="n">
-        <v>5173</v>
+        <v>90857</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2499,43 +2484,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697273</v>
+        <v>697191</v>
       </c>
       <c r="R17" t="n">
-        <v>6557108</v>
+        <v>6557040</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2567,7 +2547,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2577,7 +2557,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2591,22 +2571,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2624,10 +2604,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540906</v>
+        <v>122540904</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>4770</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2640,27 +2620,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2669,10 +2649,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697226</v>
+        <v>697224</v>
       </c>
       <c r="R18" t="n">
-        <v>6557113</v>
+        <v>6557123</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2704,7 +2684,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2714,7 +2694,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2728,22 +2708,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Björklåga med barken kvar.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Betula # Björklåga med barken kvar.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2761,10 +2741,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540904</v>
+        <v>122540902</v>
       </c>
       <c r="B19" t="n">
-        <v>4770</v>
+        <v>5489</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2773,25 +2753,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100299</v>
+        <v>101410</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2806,10 +2786,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697224</v>
+        <v>697275</v>
       </c>
       <c r="R19" t="n">
-        <v>6557123</v>
+        <v>6557207</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2841,7 +2821,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2851,7 +2831,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2865,22 +2845,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2898,10 +2878,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540899</v>
+        <v>122540915</v>
       </c>
       <c r="B20" t="n">
-        <v>5172</v>
+        <v>4776</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2910,25 +2890,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102204</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2943,10 +2923,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697273</v>
+        <v>697173</v>
       </c>
       <c r="R20" t="n">
-        <v>6557108</v>
+        <v>6557042</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2978,7 +2958,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2988,7 +2968,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3012,12 +2992,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3035,10 +3015,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540910</v>
+        <v>122540906</v>
       </c>
       <c r="B21" t="n">
-        <v>90854</v>
+        <v>8430</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3047,38 +3027,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697191</v>
+        <v>697226</v>
       </c>
       <c r="R21" t="n">
-        <v>6557040</v>
+        <v>6557113</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3110,7 +3095,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3120,7 +3105,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3134,22 +3119,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Äldre levande tall.</t>
+          <t>Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
+          <t>Betula # Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3167,10 +3152,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540903</v>
+        <v>122540913</v>
       </c>
       <c r="B22" t="n">
-        <v>57400</v>
+        <v>4776</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3179,31 +3164,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3212,10 +3197,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697256</v>
+        <v>697178</v>
       </c>
       <c r="R22" t="n">
-        <v>6557166</v>
+        <v>6557046</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3247,7 +3232,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3257,12 +3242,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3273,6 +3253,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3289,10 +3289,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122540916</v>
+        <v>122540901</v>
       </c>
       <c r="B23" t="n">
-        <v>94762</v>
+        <v>5193</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3305,34 +3305,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697167</v>
+        <v>697273</v>
       </c>
       <c r="R23" t="n">
-        <v>6557035</v>
+        <v>6557108</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3364,7 +3369,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3374,7 +3379,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3385,6 +3390,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3401,10 +3426,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540913</v>
+        <v>122540907</v>
       </c>
       <c r="B24" t="n">
-        <v>4776</v>
+        <v>94765</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3417,39 +3442,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>2818</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697178</v>
+        <v>697232</v>
       </c>
       <c r="R24" t="n">
-        <v>6557046</v>
+        <v>6557085</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3481,7 +3501,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3491,7 +3511,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3502,26 +3522,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3541,7 +3541,7 @@
         <v>122540912</v>
       </c>
       <c r="B25" t="n">
-        <v>90854</v>
+        <v>90857</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3670,10 +3670,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540907</v>
+        <v>122540916</v>
       </c>
       <c r="B26" t="n">
-        <v>94762</v>
+        <v>94765</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697232</v>
+        <v>697167</v>
       </c>
       <c r="R26" t="n">
-        <v>6557085</v>
+        <v>6557035</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3785,7 +3785,7 @@
         <v>122540909</v>
       </c>
       <c r="B27" t="n">
-        <v>94762</v>
+        <v>94765</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>122540905</v>
       </c>
       <c r="B28" t="n">
-        <v>95012</v>
+        <v>95015</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>122318675</v>
       </c>
       <c r="B29" t="n">
-        <v>97198</v>
+        <v>97201</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122319351</v>
+        <v>122319726</v>
       </c>
       <c r="B2" t="n">
         <v>98244</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697254</v>
+        <v>697259</v>
       </c>
       <c r="R2" t="n">
-        <v>6557157</v>
+        <v>6557169</v>
       </c>
       <c r="S2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122319322</v>
+        <v>122319795</v>
       </c>
       <c r="B3" t="n">
         <v>98244</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697280</v>
+        <v>697243</v>
       </c>
       <c r="R3" t="n">
-        <v>6557133</v>
+        <v>6557191</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122318867</v>
+        <v>122320250</v>
       </c>
       <c r="B4" t="n">
-        <v>97198</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697230</v>
+        <v>697229</v>
       </c>
       <c r="R4" t="n">
-        <v>6557010</v>
+        <v>6557114</v>
       </c>
       <c r="S4" t="n">
         <v>12</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122319795</v>
+        <v>122318956</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>90857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,31 +1035,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697243</v>
+        <v>697249</v>
       </c>
       <c r="R5" t="n">
-        <v>6557191</v>
+        <v>6557062</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122319074</v>
+        <v>122319322</v>
       </c>
       <c r="B6" t="n">
-        <v>4776</v>
+        <v>98244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,36 +1154,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1188,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697255</v>
+        <v>697280</v>
       </c>
       <c r="R6" t="n">
-        <v>6557107</v>
+        <v>6557133</v>
       </c>
       <c r="S6" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122319380</v>
+        <v>122319415</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
+        <v>110382</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,25 +1270,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697263</v>
+        <v>697258</v>
       </c>
       <c r="R7" t="n">
-        <v>6557128</v>
+        <v>6557147</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122319415</v>
+        <v>122319074</v>
       </c>
       <c r="B8" t="n">
-        <v>110382</v>
+        <v>4776</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,27 +1390,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219711</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1420,13 +1423,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697258</v>
+        <v>697255</v>
       </c>
       <c r="R8" t="n">
-        <v>6557147</v>
+        <v>6557107</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,7 +1495,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122319726</v>
+        <v>122319351</v>
       </c>
       <c r="B9" t="n">
         <v>98244</v>
@@ -1536,13 +1539,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697259</v>
+        <v>697254</v>
       </c>
       <c r="R9" t="n">
-        <v>6557169</v>
+        <v>6557157</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1571,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122318956</v>
+        <v>122319380</v>
       </c>
       <c r="B10" t="n">
-        <v>90857</v>
+        <v>98244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,34 +1623,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697249</v>
+        <v>697263</v>
       </c>
       <c r="R10" t="n">
-        <v>6557062</v>
+        <v>6557128</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122320250</v>
+        <v>122318867</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>97198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,25 +1855,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697229</v>
+        <v>697230</v>
       </c>
       <c r="R12" t="n">
-        <v>6557114</v>
+        <v>6557010</v>
       </c>
       <c r="S12" t="n">
         <v>12</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122540900</v>
+        <v>122540913</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>4776</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2092,21 +2092,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697273</v>
+        <v>697178</v>
       </c>
       <c r="R14" t="n">
-        <v>6557108</v>
+        <v>6557046</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2213,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122540903</v>
+        <v>122540899</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>5172</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,27 +2229,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697256</v>
+        <v>697273</v>
       </c>
       <c r="R15" t="n">
-        <v>6557166</v>
+        <v>6557108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2303,12 +2303,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2319,6 +2314,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2335,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540899</v>
+        <v>122540906</v>
       </c>
       <c r="B16" t="n">
-        <v>5172</v>
+        <v>8430</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,31 +2362,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102204</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2380,10 +2395,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697273</v>
+        <v>697226</v>
       </c>
       <c r="R16" t="n">
-        <v>6557108</v>
+        <v>6557113</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2415,7 +2430,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2425,7 +2440,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,22 +2454,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Betula # Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2472,10 +2487,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122540910</v>
+        <v>122540901</v>
       </c>
       <c r="B17" t="n">
-        <v>90857</v>
+        <v>5193</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,38 +2499,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697191</v>
+        <v>697273</v>
       </c>
       <c r="R17" t="n">
-        <v>6557040</v>
+        <v>6557108</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2547,7 +2567,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2557,7 +2577,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2571,22 +2591,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Äldre levande tall.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2604,10 +2624,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540904</v>
+        <v>122540903</v>
       </c>
       <c r="B18" t="n">
-        <v>4770</v>
+        <v>57400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2616,31 +2636,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2649,10 +2669,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697224</v>
+        <v>697256</v>
       </c>
       <c r="R18" t="n">
-        <v>6557123</v>
+        <v>6557166</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2684,7 +2704,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2694,7 +2714,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2705,26 +2730,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2741,10 +2746,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540902</v>
+        <v>122540910</v>
       </c>
       <c r="B19" t="n">
-        <v>5489</v>
+        <v>90857</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2757,39 +2762,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101410</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697275</v>
+        <v>697191</v>
       </c>
       <c r="R19" t="n">
-        <v>6557207</v>
+        <v>6557040</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Gammal levande tall med flagnad bark.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540915</v>
+        <v>122540904</v>
       </c>
       <c r="B20" t="n">
-        <v>4776</v>
+        <v>4770</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2894,21 +2894,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697173</v>
+        <v>697224</v>
       </c>
       <c r="R20" t="n">
-        <v>6557042</v>
+        <v>6557123</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540906</v>
+        <v>122540912</v>
       </c>
       <c r="B21" t="n">
-        <v>8430</v>
+        <v>90857</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3027,43 +3027,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697226</v>
+        <v>697180</v>
       </c>
       <c r="R21" t="n">
-        <v>6557113</v>
+        <v>6557049</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3095,7 +3090,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3105,7 +3100,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3119,22 +3114,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Björklåga med barken kvar.</t>
+          <t>Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Betula # Björklåga med barken kvar.</t>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3152,7 +3147,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540913</v>
+        <v>122540915</v>
       </c>
       <c r="B22" t="n">
         <v>4776</v>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697178</v>
+        <v>697173</v>
       </c>
       <c r="R22" t="n">
-        <v>6557046</v>
+        <v>6557042</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3232,7 +3227,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3242,7 +3237,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3289,10 +3284,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122540901</v>
+        <v>122540907</v>
       </c>
       <c r="B23" t="n">
-        <v>5193</v>
+        <v>94765</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3305,39 +3300,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697273</v>
+        <v>697232</v>
       </c>
       <c r="R23" t="n">
-        <v>6557108</v>
+        <v>6557085</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3369,7 +3359,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3379,7 +3369,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3390,26 +3380,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3426,10 +3396,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540907</v>
+        <v>122540902</v>
       </c>
       <c r="B24" t="n">
-        <v>94765</v>
+        <v>5489</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3438,38 +3408,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2818</v>
+        <v>101410</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697232</v>
+        <v>697275</v>
       </c>
       <c r="R24" t="n">
-        <v>6557085</v>
+        <v>6557207</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3501,7 +3476,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3511,7 +3486,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3522,6 +3497,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Gammal levande tall med flagnad bark.</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3538,10 +3533,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122540912</v>
+        <v>122540900</v>
       </c>
       <c r="B25" t="n">
-        <v>90857</v>
+        <v>5173</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3550,38 +3545,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697180</v>
+        <v>697273</v>
       </c>
       <c r="R25" t="n">
-        <v>6557049</v>
+        <v>6557108</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3637,22 +3637,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540909</v>
+        <v>122540905</v>
       </c>
       <c r="B27" t="n">
-        <v>94765</v>
+        <v>95015</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697191</v>
+        <v>697222</v>
       </c>
       <c r="R27" t="n">
-        <v>6557038</v>
+        <v>6557122</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3894,10 +3894,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540905</v>
+        <v>122540909</v>
       </c>
       <c r="B28" t="n">
-        <v>95015</v>
+        <v>94765</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697222</v>
+        <v>697191</v>
       </c>
       <c r="R28" t="n">
-        <v>6557122</v>
+        <v>6557038</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4121,6 +4121,138 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122726917</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91055</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1618</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Hängticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Postia ceriflua</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lekarvik, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>697197</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6557044</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>På undersidan av raftigt nedbruten granlåga.</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies # På undersidan av raftigt nedbruten granlåga.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Karin Engshagen, Kalle Skarin, Birgitta Tulin, Åsa Back</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -3015,10 +3015,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540912</v>
+        <v>122540915</v>
       </c>
       <c r="B21" t="n">
-        <v>90857</v>
+        <v>4776</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3027,38 +3027,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697180</v>
+        <v>697173</v>
       </c>
       <c r="R21" t="n">
-        <v>6557049</v>
+        <v>6557042</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3090,7 +3095,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3100,7 +3105,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3114,22 +3119,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3147,10 +3152,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540915</v>
+        <v>122540912</v>
       </c>
       <c r="B22" t="n">
-        <v>4776</v>
+        <v>90857</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3159,43 +3164,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697173</v>
+        <v>697180</v>
       </c>
       <c r="R22" t="n">
-        <v>6557042</v>
+        <v>6557049</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,22 +3251,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -3015,10 +3015,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540915</v>
+        <v>122540912</v>
       </c>
       <c r="B21" t="n">
-        <v>4776</v>
+        <v>90857</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3027,43 +3027,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697173</v>
+        <v>697180</v>
       </c>
       <c r="R21" t="n">
-        <v>6557042</v>
+        <v>6557049</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3095,7 +3090,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3105,7 +3100,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3119,22 +3114,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3152,10 +3147,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540912</v>
+        <v>122540915</v>
       </c>
       <c r="B22" t="n">
-        <v>90857</v>
+        <v>4776</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3164,38 +3159,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697180</v>
+        <v>697173</v>
       </c>
       <c r="R22" t="n">
-        <v>6557049</v>
+        <v>6557042</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,22 +3251,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -2076,7 +2076,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122540913</v>
+        <v>122540915</v>
       </c>
       <c r="B14" t="n">
         <v>4776</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697178</v>
+        <v>697173</v>
       </c>
       <c r="R14" t="n">
-        <v>6557046</v>
+        <v>6557042</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122540899</v>
+        <v>122540901</v>
       </c>
       <c r="B15" t="n">
-        <v>5172</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,25 +2225,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102204</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540906</v>
+        <v>122540899</v>
       </c>
       <c r="B16" t="n">
-        <v>8430</v>
+        <v>5172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2362,31 +2362,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>102204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697226</v>
+        <v>697273</v>
       </c>
       <c r="R16" t="n">
-        <v>6557113</v>
+        <v>6557108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Björklåga med barken kvar.</t>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Betula # Björklåga med barken kvar.</t>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122540901</v>
+        <v>122540916</v>
       </c>
       <c r="B17" t="n">
-        <v>5193</v>
+        <v>94868</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2503,39 +2503,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697273</v>
+        <v>697167</v>
       </c>
       <c r="R17" t="n">
-        <v>6557108</v>
+        <v>6557035</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2567,7 +2562,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2577,7 +2572,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2588,26 +2583,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2624,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540903</v>
+        <v>122540906</v>
       </c>
       <c r="B18" t="n">
-        <v>57400</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2636,31 +2611,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2669,10 +2644,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697256</v>
+        <v>697226</v>
       </c>
       <c r="R18" t="n">
-        <v>6557166</v>
+        <v>6557113</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2704,7 +2679,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2714,12 +2689,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2730,6 +2700,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Björklåga med barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Betula # Björklåga med barken kvar.</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2746,10 +2736,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540910</v>
+        <v>122540903</v>
       </c>
       <c r="B19" t="n">
-        <v>90857</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2762,34 +2752,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697191</v>
+        <v>697256</v>
       </c>
       <c r="R19" t="n">
-        <v>6557040</v>
+        <v>6557166</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2821,7 +2816,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2831,7 +2826,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,26 +2842,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Äldre levande tall.</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2878,10 +2858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540904</v>
+        <v>122540912</v>
       </c>
       <c r="B20" t="n">
-        <v>4770</v>
+        <v>90960</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2890,43 +2870,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100299</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697224</v>
+        <v>697180</v>
       </c>
       <c r="R20" t="n">
-        <v>6557123</v>
+        <v>6557049</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2958,7 +2933,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2968,7 +2943,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2982,22 +2957,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3015,10 +2990,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540915</v>
+        <v>122540907</v>
       </c>
       <c r="B21" t="n">
-        <v>4776</v>
+        <v>94868</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3031,39 +3006,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697173</v>
+        <v>697232</v>
       </c>
       <c r="R21" t="n">
-        <v>6557042</v>
+        <v>6557085</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3095,7 +3065,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3105,7 +3075,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3116,26 +3086,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3152,10 +3102,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540912</v>
+        <v>122540913</v>
       </c>
       <c r="B22" t="n">
-        <v>90857</v>
+        <v>4776</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3164,38 +3114,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697180</v>
+        <v>697178</v>
       </c>
       <c r="R22" t="n">
-        <v>6557049</v>
+        <v>6557046</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3227,7 +3182,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3237,7 +3192,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,22 +3206,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3284,10 +3239,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122540907</v>
+        <v>122540900</v>
       </c>
       <c r="B23" t="n">
-        <v>94765</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3300,34 +3255,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697232</v>
+        <v>697273</v>
       </c>
       <c r="R23" t="n">
-        <v>6557085</v>
+        <v>6557108</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3359,7 +3319,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3369,7 +3329,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3380,6 +3340,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3396,10 +3376,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540902</v>
+        <v>122540904</v>
       </c>
       <c r="B24" t="n">
-        <v>5489</v>
+        <v>4770</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3408,25 +3388,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101410</v>
+        <v>100299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3441,10 +3421,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697275</v>
+        <v>697224</v>
       </c>
       <c r="R24" t="n">
-        <v>6557207</v>
+        <v>6557123</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3476,7 +3456,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3486,7 +3466,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3500,22 +3480,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Gammal levande tall med flagnad bark.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3533,10 +3513,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122540900</v>
+        <v>122540910</v>
       </c>
       <c r="B25" t="n">
-        <v>5173</v>
+        <v>90960</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3545,43 +3525,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697273</v>
+        <v>697191</v>
       </c>
       <c r="R25" t="n">
-        <v>6557108</v>
+        <v>6557040</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3613,7 +3588,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3623,7 +3598,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3637,22 +3612,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3670,10 +3645,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540916</v>
+        <v>122540902</v>
       </c>
       <c r="B26" t="n">
-        <v>94765</v>
+        <v>5489</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3682,38 +3657,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2818</v>
+        <v>101410</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697167</v>
+        <v>697275</v>
       </c>
       <c r="R26" t="n">
-        <v>6557035</v>
+        <v>6557207</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3745,7 +3725,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3755,7 +3735,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3766,6 +3746,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Gammal levande tall med flagnad bark.</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3782,10 +3782,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540905</v>
+        <v>122540909</v>
       </c>
       <c r="B27" t="n">
-        <v>95015</v>
+        <v>94868</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697222</v>
+        <v>697191</v>
       </c>
       <c r="R27" t="n">
-        <v>6557122</v>
+        <v>6557038</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3894,10 +3894,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540909</v>
+        <v>122540905</v>
       </c>
       <c r="B28" t="n">
-        <v>94765</v>
+        <v>95118</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697191</v>
+        <v>697222</v>
       </c>
       <c r="R28" t="n">
-        <v>6557038</v>
+        <v>6557122</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4009,7 +4009,7 @@
         <v>122318675</v>
       </c>
       <c r="B29" t="n">
-        <v>97201</v>
+        <v>97304</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>122726917</v>
       </c>
       <c r="B30" t="n">
-        <v>91055</v>
+        <v>91158</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -2736,10 +2736,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540903</v>
+        <v>122540912</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>90960</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2752,39 +2752,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697256</v>
+        <v>697180</v>
       </c>
       <c r="R19" t="n">
-        <v>6557166</v>
+        <v>6557049</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2816,7 +2811,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2826,12 +2821,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,6 +2832,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Klen äldre levande tall.</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2858,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540912</v>
+        <v>122540903</v>
       </c>
       <c r="B20" t="n">
-        <v>90960</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2874,34 +2884,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697180</v>
+        <v>697256</v>
       </c>
       <c r="R20" t="n">
-        <v>6557049</v>
+        <v>6557166</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2933,7 +2948,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2943,7 +2958,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2954,26 +2974,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Klen äldre levande tall.</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -2736,10 +2736,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540912</v>
+        <v>122540903</v>
       </c>
       <c r="B19" t="n">
-        <v>90960</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2752,34 +2752,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697180</v>
+        <v>697256</v>
       </c>
       <c r="R19" t="n">
-        <v>6557049</v>
+        <v>6557166</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2811,7 +2816,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2821,7 +2826,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2832,26 +2842,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Klen äldre levande tall.</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2868,10 +2858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540903</v>
+        <v>122540912</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>90960</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,39 +2874,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697256</v>
+        <v>697180</v>
       </c>
       <c r="R20" t="n">
-        <v>6557166</v>
+        <v>6557049</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2948,7 +2933,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2958,12 +2943,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2974,6 +2954,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Klen äldre levande tall.</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -4126,7 +4126,7 @@
         <v>122726917</v>
       </c>
       <c r="B30" t="n">
-        <v>91158</v>
+        <v>91162</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122540915</v>
+        <v>122540910</v>
       </c>
       <c r="B14" t="n">
-        <v>4776</v>
+        <v>90964</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,43 +2088,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697173</v>
+        <v>697191</v>
       </c>
       <c r="R14" t="n">
-        <v>6557042</v>
+        <v>6557040</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,22 +2175,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2213,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122540901</v>
+        <v>122540904</v>
       </c>
       <c r="B15" t="n">
-        <v>5193</v>
+        <v>4770</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,21 +2224,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2258,10 +2253,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697273</v>
+        <v>697224</v>
       </c>
       <c r="R15" t="n">
-        <v>6557108</v>
+        <v>6557123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2303,7 +2298,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,10 +2345,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540899</v>
+        <v>122540913</v>
       </c>
       <c r="B16" t="n">
-        <v>5172</v>
+        <v>4776</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2362,25 +2357,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102204</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2395,10 +2390,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697273</v>
+        <v>697178</v>
       </c>
       <c r="R16" t="n">
-        <v>6557108</v>
+        <v>6557046</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,7 +2425,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2440,7 +2435,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2464,12 +2459,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2487,10 +2482,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122540916</v>
+        <v>122540903</v>
       </c>
       <c r="B17" t="n">
-        <v>94868</v>
+        <v>57494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2499,38 +2494,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697167</v>
+        <v>697256</v>
       </c>
       <c r="R17" t="n">
-        <v>6557035</v>
+        <v>6557166</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2572,7 +2572,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2599,10 +2604,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540906</v>
+        <v>122540907</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>94876</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,39 +2620,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697226</v>
+        <v>697232</v>
       </c>
       <c r="R18" t="n">
-        <v>6557113</v>
+        <v>6557085</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,26 +2700,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Björklåga med barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Betula # Björklåga med barken kvar.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2736,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540903</v>
+        <v>122540901</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>5193</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2748,20 +2728,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2772,7 +2752,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2781,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697256</v>
+        <v>697273</v>
       </c>
       <c r="R19" t="n">
-        <v>6557166</v>
+        <v>6557108</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2816,7 +2796,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2826,12 +2806,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,6 +2817,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2858,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540912</v>
+        <v>122540915</v>
       </c>
       <c r="B20" t="n">
-        <v>90960</v>
+        <v>4776</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2870,38 +2865,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697180</v>
+        <v>697173</v>
       </c>
       <c r="R20" t="n">
-        <v>6557049</v>
+        <v>6557042</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540907</v>
+        <v>122540906</v>
       </c>
       <c r="B21" t="n">
-        <v>94868</v>
+        <v>8430</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3006,34 +3006,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2818</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697232</v>
+        <v>697226</v>
       </c>
       <c r="R21" t="n">
-        <v>6557085</v>
+        <v>6557113</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3065,7 +3070,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3075,7 +3080,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3086,6 +3091,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Björklåga med barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Betula # Björklåga med barken kvar.</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3102,10 +3127,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540913</v>
+        <v>122540900</v>
       </c>
       <c r="B22" t="n">
-        <v>4776</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3118,21 +3143,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3147,10 +3172,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697178</v>
+        <v>697273</v>
       </c>
       <c r="R22" t="n">
-        <v>6557046</v>
+        <v>6557108</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3182,7 +3207,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3192,7 +3217,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3216,12 +3241,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3239,10 +3264,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122540900</v>
+        <v>122540912</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>90964</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3251,43 +3276,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697273</v>
+        <v>697180</v>
       </c>
       <c r="R23" t="n">
-        <v>6557108</v>
+        <v>6557049</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3319,7 +3339,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3329,7 +3349,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3343,22 +3363,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3376,10 +3396,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540904</v>
+        <v>122540899</v>
       </c>
       <c r="B24" t="n">
-        <v>4770</v>
+        <v>5172</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3388,25 +3408,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100299</v>
+        <v>102204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3421,10 +3441,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697224</v>
+        <v>697273</v>
       </c>
       <c r="R24" t="n">
-        <v>6557123</v>
+        <v>6557108</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3456,7 +3476,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3466,7 +3486,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3490,12 +3510,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3513,10 +3533,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122540910</v>
+        <v>122540902</v>
       </c>
       <c r="B25" t="n">
-        <v>90960</v>
+        <v>5489</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3529,34 +3549,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>101410</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697191</v>
+        <v>697275</v>
       </c>
       <c r="R25" t="n">
-        <v>6557040</v>
+        <v>6557207</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3588,7 +3613,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3598,7 +3623,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3622,12 +3647,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Äldre levande tall.</t>
+          <t>Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3645,10 +3670,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540902</v>
+        <v>122540916</v>
       </c>
       <c r="B26" t="n">
-        <v>5489</v>
+        <v>94876</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3657,43 +3682,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101410</v>
+        <v>2818</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697275</v>
+        <v>697167</v>
       </c>
       <c r="R26" t="n">
-        <v>6557207</v>
+        <v>6557035</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3725,7 +3745,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3735,7 +3755,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3746,26 +3766,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Gammal levande tall med flagnad bark.</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3782,10 +3782,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540909</v>
+        <v>122540905</v>
       </c>
       <c r="B27" t="n">
-        <v>94868</v>
+        <v>95126</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697191</v>
+        <v>697222</v>
       </c>
       <c r="R27" t="n">
-        <v>6557038</v>
+        <v>6557122</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3894,10 +3894,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540905</v>
+        <v>122540909</v>
       </c>
       <c r="B28" t="n">
-        <v>95118</v>
+        <v>94876</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697222</v>
+        <v>697191</v>
       </c>
       <c r="R28" t="n">
-        <v>6557122</v>
+        <v>6557038</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4009,7 +4009,7 @@
         <v>122318675</v>
       </c>
       <c r="B29" t="n">
-        <v>97304</v>
+        <v>97312</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122540910</v>
+        <v>122540902</v>
       </c>
       <c r="B14" t="n">
-        <v>90964</v>
+        <v>5489</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2092,34 +2092,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>101410</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697191</v>
+        <v>697275</v>
       </c>
       <c r="R14" t="n">
-        <v>6557040</v>
+        <v>6557207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,7 +2166,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,12 +2190,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Äldre levande tall.</t>
+          <t>Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2208,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122540904</v>
+        <v>122540916</v>
       </c>
       <c r="B15" t="n">
-        <v>4770</v>
+        <v>94876</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,39 +2229,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100299</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697224</v>
+        <v>697167</v>
       </c>
       <c r="R15" t="n">
-        <v>6557123</v>
+        <v>6557035</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,26 +2309,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2345,10 +2325,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540913</v>
+        <v>122540899</v>
       </c>
       <c r="B16" t="n">
-        <v>4776</v>
+        <v>5172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2357,25 +2337,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>102204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2390,10 +2370,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697178</v>
+        <v>697273</v>
       </c>
       <c r="R16" t="n">
-        <v>6557046</v>
+        <v>6557108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2425,7 +2405,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2435,7 +2415,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2459,12 +2439,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2482,10 +2462,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122540903</v>
+        <v>122540904</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>4770</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2494,31 +2474,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2527,10 +2507,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697256</v>
+        <v>697224</v>
       </c>
       <c r="R17" t="n">
-        <v>6557166</v>
+        <v>6557123</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2562,7 +2542,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2572,12 +2552,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2588,6 +2563,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2604,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540907</v>
+        <v>122540906</v>
       </c>
       <c r="B18" t="n">
-        <v>94876</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2620,34 +2615,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697232</v>
+        <v>697226</v>
       </c>
       <c r="R18" t="n">
-        <v>6557085</v>
+        <v>6557113</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,6 +2700,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Björklåga med barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Betula # Björklåga med barken kvar.</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2716,10 +2736,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540901</v>
+        <v>122540910</v>
       </c>
       <c r="B19" t="n">
-        <v>5193</v>
+        <v>90964</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,43 +2748,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697273</v>
+        <v>697191</v>
       </c>
       <c r="R19" t="n">
-        <v>6557108</v>
+        <v>6557040</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2796,7 +2811,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2806,7 +2821,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,22 +2835,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2853,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540915</v>
+        <v>122540903</v>
       </c>
       <c r="B20" t="n">
-        <v>4776</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,31 +2880,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2898,10 +2913,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697173</v>
+        <v>697256</v>
       </c>
       <c r="R20" t="n">
-        <v>6557042</v>
+        <v>6557166</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2933,7 +2948,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2943,7 +2958,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2954,26 +2974,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2990,10 +2990,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540906</v>
+        <v>122540915</v>
       </c>
       <c r="B21" t="n">
-        <v>8430</v>
+        <v>4776</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3006,27 +3006,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697226</v>
+        <v>697173</v>
       </c>
       <c r="R21" t="n">
-        <v>6557113</v>
+        <v>6557042</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Björklåga med barken kvar.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Betula # Björklåga med barken kvar.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3127,10 +3127,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540900</v>
+        <v>122540907</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>94876</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3143,39 +3143,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697273</v>
+        <v>697232</v>
       </c>
       <c r="R22" t="n">
-        <v>6557108</v>
+        <v>6557085</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3207,7 +3202,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3217,7 +3212,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3228,26 +3223,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3264,10 +3239,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122540912</v>
+        <v>122540901</v>
       </c>
       <c r="B23" t="n">
-        <v>90964</v>
+        <v>5193</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3276,38 +3251,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697180</v>
+        <v>697273</v>
       </c>
       <c r="R23" t="n">
-        <v>6557049</v>
+        <v>6557108</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3339,7 +3319,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3349,7 +3329,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3363,22 +3343,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3396,10 +3376,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540899</v>
+        <v>122540900</v>
       </c>
       <c r="B24" t="n">
-        <v>5172</v>
+        <v>5173</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3408,25 +3388,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102204</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3510,12 +3490,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3533,10 +3513,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122540902</v>
+        <v>122540913</v>
       </c>
       <c r="B25" t="n">
-        <v>5489</v>
+        <v>4776</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3545,25 +3525,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101410</v>
+        <v>102306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3578,10 +3558,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697275</v>
+        <v>697178</v>
       </c>
       <c r="R25" t="n">
-        <v>6557207</v>
+        <v>6557046</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3613,7 +3593,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3623,7 +3603,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3637,22 +3617,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Gammal levande tall med flagnad bark.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3670,10 +3650,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540916</v>
+        <v>122540912</v>
       </c>
       <c r="B26" t="n">
-        <v>94876</v>
+        <v>90964</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3682,25 +3662,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2818</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3710,10 +3690,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697167</v>
+        <v>697180</v>
       </c>
       <c r="R26" t="n">
-        <v>6557035</v>
+        <v>6557049</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3745,7 +3725,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3755,7 +3735,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3766,6 +3746,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Klen äldre levande tall.</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3782,10 +3782,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540905</v>
+        <v>122540909</v>
       </c>
       <c r="B27" t="n">
-        <v>95126</v>
+        <v>94876</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697222</v>
+        <v>697191</v>
       </c>
       <c r="R27" t="n">
-        <v>6557122</v>
+        <v>6557038</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3894,10 +3894,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540909</v>
+        <v>122540905</v>
       </c>
       <c r="B28" t="n">
-        <v>94876</v>
+        <v>95126</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697191</v>
+        <v>697222</v>
       </c>
       <c r="R28" t="n">
-        <v>6557038</v>
+        <v>6557122</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -2213,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122540916</v>
+        <v>122540912</v>
       </c>
       <c r="B15" t="n">
-        <v>94876</v>
+        <v>90964</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,25 +2225,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697167</v>
+        <v>697180</v>
       </c>
       <c r="R15" t="n">
-        <v>6557035</v>
+        <v>6557049</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,6 +2309,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Klen äldre levande tall.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2325,10 +2345,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540899</v>
+        <v>122540910</v>
       </c>
       <c r="B16" t="n">
-        <v>5172</v>
+        <v>90964</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2341,39 +2361,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102204</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697273</v>
+        <v>697191</v>
       </c>
       <c r="R16" t="n">
-        <v>6557108</v>
+        <v>6557040</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,7 +2420,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2415,7 +2430,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,22 +2444,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2462,10 +2477,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122540904</v>
+        <v>122540916</v>
       </c>
       <c r="B17" t="n">
-        <v>4770</v>
+        <v>94878</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2478,39 +2493,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100299</v>
+        <v>2818</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697224</v>
+        <v>697167</v>
       </c>
       <c r="R17" t="n">
-        <v>6557123</v>
+        <v>6557035</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2542,7 +2552,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2552,7 +2562,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2563,26 +2573,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2599,10 +2589,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540906</v>
+        <v>122540903</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2611,31 +2601,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2644,10 +2634,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697226</v>
+        <v>697256</v>
       </c>
       <c r="R18" t="n">
-        <v>6557113</v>
+        <v>6557166</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2679,7 +2669,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2689,7 +2679,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,26 +2695,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Björklåga med barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Betula # Björklåga med barken kvar.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2736,10 +2711,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540910</v>
+        <v>122540915</v>
       </c>
       <c r="B19" t="n">
-        <v>90964</v>
+        <v>4776</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2748,38 +2723,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697191</v>
+        <v>697173</v>
       </c>
       <c r="R19" t="n">
-        <v>6557040</v>
+        <v>6557042</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2811,7 +2791,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2821,7 +2801,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2835,22 +2815,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Äldre levande tall.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2868,10 +2848,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540903</v>
+        <v>122540913</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>4776</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2880,31 +2860,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2913,10 +2893,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697256</v>
+        <v>697178</v>
       </c>
       <c r="R20" t="n">
-        <v>6557166</v>
+        <v>6557046</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2948,7 +2928,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2958,12 +2938,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2974,6 +2949,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2990,10 +2985,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540915</v>
+        <v>122540907</v>
       </c>
       <c r="B21" t="n">
-        <v>4776</v>
+        <v>94878</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3006,39 +3001,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697173</v>
+        <v>697232</v>
       </c>
       <c r="R21" t="n">
-        <v>6557042</v>
+        <v>6557085</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3070,7 +3060,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3080,7 +3070,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3091,26 +3081,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3127,10 +3097,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540907</v>
+        <v>122540904</v>
       </c>
       <c r="B22" t="n">
-        <v>94876</v>
+        <v>4770</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3143,34 +3113,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2818</v>
+        <v>100299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697232</v>
+        <v>697224</v>
       </c>
       <c r="R22" t="n">
-        <v>6557085</v>
+        <v>6557123</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3202,7 +3177,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3212,7 +3187,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3223,6 +3198,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3239,10 +3234,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122540901</v>
+        <v>122540906</v>
       </c>
       <c r="B23" t="n">
-        <v>5193</v>
+        <v>8430</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3255,27 +3250,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3284,10 +3279,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697273</v>
+        <v>697226</v>
       </c>
       <c r="R23" t="n">
-        <v>6557108</v>
+        <v>6557113</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3319,7 +3314,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3329,7 +3324,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3343,22 +3338,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Betula # Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3376,10 +3371,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540900</v>
+        <v>122540901</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3392,21 +3387,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3490,12 +3485,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3513,10 +3508,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122540913</v>
+        <v>122540900</v>
       </c>
       <c r="B25" t="n">
-        <v>4776</v>
+        <v>5173</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3529,21 +3524,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3558,10 +3553,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697178</v>
+        <v>697273</v>
       </c>
       <c r="R25" t="n">
-        <v>6557046</v>
+        <v>6557108</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3593,7 +3588,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3603,7 +3598,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3627,12 +3622,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3650,10 +3645,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122540912</v>
+        <v>122540899</v>
       </c>
       <c r="B26" t="n">
-        <v>90964</v>
+        <v>5172</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3666,34 +3661,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>102204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697180</v>
+        <v>697273</v>
       </c>
       <c r="R26" t="n">
-        <v>6557049</v>
+        <v>6557108</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3749,22 +3749,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Picea abies # Tillsammans med bronshjon på klen grallåga utan bark.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122540909</v>
+        <v>122540905</v>
       </c>
       <c r="B27" t="n">
-        <v>94876</v>
+        <v>95128</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697191</v>
+        <v>697222</v>
       </c>
       <c r="R27" t="n">
-        <v>6557038</v>
+        <v>6557122</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3894,10 +3894,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122540905</v>
+        <v>122540909</v>
       </c>
       <c r="B28" t="n">
-        <v>95126</v>
+        <v>94878</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697222</v>
+        <v>697191</v>
       </c>
       <c r="R28" t="n">
-        <v>6557122</v>
+        <v>6557038</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4009,7 +4009,7 @@
         <v>122318675</v>
       </c>
       <c r="B29" t="n">
-        <v>97312</v>
+        <v>97314</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122540902</v>
+        <v>122540912</v>
       </c>
       <c r="B14" t="n">
-        <v>5489</v>
+        <v>90964</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2092,39 +2092,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101410</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697275</v>
+        <v>697180</v>
       </c>
       <c r="R14" t="n">
-        <v>6557207</v>
+        <v>6557049</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,12 +2185,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Gammal levande tall med flagnad bark.</t>
+          <t>Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2213,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122540912</v>
+        <v>122540902</v>
       </c>
       <c r="B15" t="n">
-        <v>90964</v>
+        <v>5489</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,34 +2224,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>101410</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697180</v>
+        <v>697275</v>
       </c>
       <c r="R15" t="n">
-        <v>6557049</v>
+        <v>6557207</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -2076,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122540912</v>
+        <v>122540900</v>
       </c>
       <c r="B14" t="n">
-        <v>90964</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,38 +2088,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697180</v>
+        <v>697273</v>
       </c>
       <c r="R14" t="n">
-        <v>6557049</v>
+        <v>6557108</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,7 +2166,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,22 +2180,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Klen äldre levande tall.</t>
+          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2208,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122540902</v>
+        <v>122540910</v>
       </c>
       <c r="B15" t="n">
-        <v>5489</v>
+        <v>90964</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,39 +2229,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101410</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697275</v>
+        <v>697191</v>
       </c>
       <c r="R15" t="n">
-        <v>6557207</v>
+        <v>6557040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Gammal levande tall med flagnad bark.</t>
+          <t>Äldre levande tall.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
+          <t>Pinus sylvestris # Äldre levande tall.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122540910</v>
+        <v>122540906</v>
       </c>
       <c r="B16" t="n">
-        <v>90964</v>
+        <v>8430</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2357,38 +2357,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697191</v>
+        <v>697226</v>
       </c>
       <c r="R16" t="n">
-        <v>6557040</v>
+        <v>6557113</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2420,7 +2425,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2430,7 +2435,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2444,22 +2449,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Äldre levande tall.</t>
+          <t>Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre levande tall.</t>
+          <t>Betula # Björklåga med barken kvar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2589,10 +2594,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122540903</v>
+        <v>122540912</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>90964</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2605,39 +2610,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697256</v>
+        <v>697180</v>
       </c>
       <c r="R18" t="n">
-        <v>6557166</v>
+        <v>6557049</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2679,12 +2679,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födosökshack på tall.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2695,6 +2690,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Klen äldre levande tall.</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Klen äldre levande tall.</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2711,10 +2726,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122540915</v>
+        <v>122540904</v>
       </c>
       <c r="B19" t="n">
-        <v>4776</v>
+        <v>4770</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2727,21 +2742,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>100299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2756,10 +2771,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697173</v>
+        <v>697224</v>
       </c>
       <c r="R19" t="n">
-        <v>6557042</v>
+        <v>6557123</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2791,7 +2806,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2801,7 +2816,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2825,12 +2840,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2848,10 +2863,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122540913</v>
+        <v>122540901</v>
       </c>
       <c r="B20" t="n">
-        <v>4776</v>
+        <v>5193</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2864,21 +2879,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2893,10 +2908,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697178</v>
+        <v>697273</v>
       </c>
       <c r="R20" t="n">
-        <v>6557046</v>
+        <v>6557108</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2928,7 +2943,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2938,7 +2953,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2962,12 +2977,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Äldre grovbarkig levande gran.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2985,10 +3000,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122540907</v>
+        <v>122540903</v>
       </c>
       <c r="B21" t="n">
-        <v>94878</v>
+        <v>57494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2997,38 +3012,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697232</v>
+        <v>697256</v>
       </c>
       <c r="R21" t="n">
-        <v>6557085</v>
+        <v>6557166</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3060,7 +3080,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3070,7 +3090,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Födosökshack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3097,10 +3122,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122540904</v>
+        <v>122540913</v>
       </c>
       <c r="B22" t="n">
-        <v>4770</v>
+        <v>4776</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3113,21 +3138,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100299</v>
+        <v>102306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3142,10 +3167,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697224</v>
+        <v>697178</v>
       </c>
       <c r="R22" t="n">
-        <v>6557123</v>
+        <v>6557046</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3177,7 +3202,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3187,7 +3212,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3211,12 +3236,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3234,10 +3259,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122540906</v>
+        <v>122540907</v>
       </c>
       <c r="B23" t="n">
-        <v>8430</v>
+        <v>94878</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3250,39 +3275,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lekarvik, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697226</v>
+        <v>697232</v>
       </c>
       <c r="R23" t="n">
-        <v>6557113</v>
+        <v>6557085</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3314,7 +3334,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3324,7 +3344,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3335,26 +3355,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Björklåga med barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Betula # Björklåga med barken kvar.</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3371,10 +3371,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122540901</v>
+        <v>122540902</v>
       </c>
       <c r="B24" t="n">
-        <v>5193</v>
+        <v>5489</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3383,25 +3383,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>101410</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697273</v>
+        <v>697275</v>
       </c>
       <c r="R24" t="n">
-        <v>6557108</v>
+        <v>6557207</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3475,22 +3475,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Pinus sylvestris # Gammal levande tall med flagnad bark.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122540900</v>
+        <v>122540915</v>
       </c>
       <c r="B25" t="n">
-        <v>5173</v>
+        <v>4776</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3524,21 +3524,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697273</v>
+        <v>697173</v>
       </c>
       <c r="R25" t="n">
-        <v>6557108</v>
+        <v>6557042</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Tillsammans med grönhjon på klen granlåga utan bark.</t>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -4009,7 +4009,7 @@
         <v>122318675</v>
       </c>
       <c r="B29" t="n">
-        <v>97314</v>
+        <v>97322</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>122726917</v>
       </c>
       <c r="B30" t="n">
-        <v>91162</v>
+        <v>91170</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 2215-2025 artfynd.xlsx
+++ b/artfynd/A 2215-2025 artfynd.xlsx
@@ -4126,7 +4126,7 @@
         <v>122726917</v>
       </c>
       <c r="B30" t="n">
-        <v>91170</v>
+        <v>91173</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
